--- a/optimized_version/metadata/validation_daily_metrics/agus4_validation_daily_metrics.xlsx
+++ b/optimized_version/metadata/validation_daily_metrics/agus4_validation_daily_metrics.xlsx
@@ -467,7 +467,7 @@
         <v>45676</v>
       </c>
       <c r="B2" t="n">
-        <v>0.2199416964538662</v>
+        <v>0.2226321950879064</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
@@ -476,10 +476,10 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2116114047006761</v>
+        <v>0.214200000698952</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2116114047006761</v>
+        <v>0.214200000698952</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
@@ -491,7 +491,7 @@
         <v>45677</v>
       </c>
       <c r="B3" t="n">
-        <v>3.108576206627558</v>
+        <v>3.108856290469382</v>
       </c>
       <c r="C3" t="n">
         <v>24</v>
@@ -500,13 +500,13 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>2.509163450331089</v>
+        <v>2.509379166724873</v>
       </c>
       <c r="F3" t="n">
-        <v>5.926159384854881</v>
+        <v>5.926175501856475</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2049446608372034</v>
+        <v>0.2049403363076855</v>
       </c>
       <c r="H3" t="n">
         <v>24</v>
@@ -517,7 +517,7 @@
         <v>45678</v>
       </c>
       <c r="B4" t="n">
-        <v>5.479017815917421</v>
+        <v>5.478969175895346</v>
       </c>
       <c r="C4" t="n">
         <v>24</v>
@@ -526,13 +526,13 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>3.890040716420462</v>
+        <v>3.889824999939858</v>
       </c>
       <c r="F4" t="n">
-        <v>9.388461464657004</v>
+        <v>9.388450136379054</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3991741605163515</v>
+        <v>0.3991756104489157</v>
       </c>
       <c r="H4" t="n">
         <v>24</v>
@@ -543,7 +543,7 @@
         <v>45679</v>
       </c>
       <c r="B5" t="n">
-        <v>0.1387789203965171</v>
+        <v>0.1381093329588311</v>
       </c>
       <c r="C5" t="n">
         <v>24</v>
@@ -552,13 +552,13 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1334554825486431</v>
+        <v>0.132808333153406</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1690742237959713</v>
+        <v>0.1692488872983076</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7419201724198122</v>
+        <v>0.7413866740638704</v>
       </c>
       <c r="H5" t="n">
         <v>24</v>
@@ -569,7 +569,7 @@
         <v>45680</v>
       </c>
       <c r="B6" t="n">
-        <v>0.1442386203712444</v>
+        <v>0.1440157209481648</v>
       </c>
       <c r="C6" t="n">
         <v>24</v>
@@ -578,13 +578,13 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1385740497537942</v>
+        <v>0.1383583332731906</v>
       </c>
       <c r="F6" t="n">
-        <v>0.161290293532191</v>
+        <v>0.1610603147308466</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03998229926994301</v>
+        <v>0.04271806607822226</v>
       </c>
       <c r="H6" t="n">
         <v>24</v>
@@ -595,7 +595,7 @@
         <v>45681</v>
       </c>
       <c r="B7" t="n">
-        <v>0.163348107456127</v>
+        <v>0.1640237582394342</v>
       </c>
       <c r="C7" t="n">
         <v>24</v>
@@ -604,13 +604,13 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1567111840719431</v>
+        <v>0.1573583335137538</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2075910740853149</v>
+        <v>0.2080286820430637</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3976819617041003</v>
+        <v>0.3951398776183513</v>
       </c>
       <c r="H7" t="n">
         <v>24</v>
@@ -621,7 +621,7 @@
         <v>45682</v>
       </c>
       <c r="B8" t="n">
-        <v>5.1082822171222</v>
+        <v>5.108929411945848</v>
       </c>
       <c r="C8" t="n">
         <v>24</v>
@@ -630,13 +630,13 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>2.38678011691287</v>
+        <v>2.386995833393474</v>
       </c>
       <c r="F8" t="n">
-        <v>10.18786477392034</v>
+        <v>10.18844310086371</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6625039269219146</v>
+        <v>0.662465609057165</v>
       </c>
       <c r="H8" t="n">
         <v>24</v>
@@ -647,7 +647,7 @@
         <v>45683</v>
       </c>
       <c r="B9" t="n">
-        <v>2.6754617654129</v>
+        <v>2.675309175210205</v>
       </c>
       <c r="C9" t="n">
         <v>24</v>
@@ -659,10 +659,10 @@
         <v>2.505262499999997</v>
       </c>
       <c r="F9" t="n">
-        <v>10.69757198199898</v>
+        <v>10.6970186627919</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05943403968557148</v>
+        <v>0.05953133648391928</v>
       </c>
       <c r="H9" t="n">
         <v>24</v>
@@ -673,7 +673,7 @@
         <v>45684</v>
       </c>
       <c r="B10" t="n">
-        <v>0.1737244551830408</v>
+        <v>0.1735797290238908</v>
       </c>
       <c r="C10" t="n">
         <v>24</v>
@@ -682,13 +682,13 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1666865497537948</v>
+        <v>0.1665458333333317</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1886681143173386</v>
+        <v>0.1885893411010168</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.799756150883709</v>
+        <v>-0.7982535866112124</v>
       </c>
       <c r="H10" t="n">
         <v>24</v>
@@ -699,7 +699,7 @@
         <v>45685</v>
       </c>
       <c r="B11" t="n">
-        <v>0.1360525838056258</v>
+        <v>0.1361325518234008</v>
       </c>
       <c r="C11" t="n">
         <v>24</v>
@@ -708,13 +708,13 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1306333333333332</v>
+        <v>0.1307083333934737</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1547250193827325</v>
+        <v>0.1546655713307715</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.343661360480097</v>
+        <v>-1.341860755288604</v>
       </c>
       <c r="H11" t="n">
         <v>24</v>
@@ -725,7 +725,7 @@
         <v>45686</v>
       </c>
       <c r="B12" t="n">
-        <v>0.1966631829874353</v>
+        <v>0.1973398658917872</v>
       </c>
       <c r="C12" t="n">
         <v>24</v>
@@ -734,13 +734,13 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1888153507386126</v>
+        <v>0.1894625001804234</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2129261850875056</v>
+        <v>0.2130467290670871</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.807850193358395</v>
+        <v>-1.811030311812595</v>
       </c>
       <c r="H12" t="n">
         <v>24</v>
@@ -751,7 +751,7 @@
         <v>45687</v>
       </c>
       <c r="B13" t="n">
-        <v>0.1693847860004974</v>
+        <v>0.169386148730038</v>
       </c>
       <c r="C13" t="n">
         <v>24</v>
@@ -763,10 +763,10 @@
         <v>0.162133333333335</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1964533728041207</v>
+        <v>0.1964990118894634</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2204653200412137</v>
+        <v>0.220103082612102</v>
       </c>
       <c r="H13" t="n">
         <v>24</v>
@@ -777,7 +777,7 @@
         <v>45688</v>
       </c>
       <c r="B14" t="n">
-        <v>0.1579856958608153</v>
+        <v>0.1579879719539322</v>
       </c>
       <c r="C14" t="n">
         <v>24</v>
@@ -789,10 +789,10 @@
         <v>0.1513208333333325</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1725867727484537</v>
+        <v>0.1724693275597243</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.4161879683623482</v>
+        <v>-0.4142611941521668</v>
       </c>
       <c r="H14" t="n">
         <v>24</v>
@@ -803,7 +803,7 @@
         <v>45689</v>
       </c>
       <c r="B15" t="n">
-        <v>0.3538860804311391</v>
+        <v>0.3541152082416876</v>
       </c>
       <c r="C15" t="n">
         <v>24</v>
@@ -812,13 +812,13 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3382009502462011</v>
+        <v>0.3384166667268046</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6610489311812784</v>
+        <v>0.6610977045942947</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.242100292603964</v>
+        <v>-1.242431157423919</v>
       </c>
       <c r="H15" t="n">
         <v>24</v>
@@ -829,7 +829,7 @@
         <v>45690</v>
       </c>
       <c r="B16" t="n">
-        <v>8.085861142718384</v>
+        <v>8.085327723082161</v>
       </c>
       <c r="C16" t="n">
         <v>24</v>
@@ -838,13 +838,13 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>4.701309649261394</v>
+        <v>4.700662499819583</v>
       </c>
       <c r="F16" t="n">
-        <v>11.31385174334851</v>
+        <v>11.3138482373548</v>
       </c>
       <c r="G16" t="n">
-        <v>0.485225164269328</v>
+        <v>0.4852254833113474</v>
       </c>
       <c r="H16" t="n">
         <v>24</v>
@@ -855,7 +855,7 @@
         <v>45691</v>
       </c>
       <c r="B17" t="n">
-        <v>0.1680026652707723</v>
+        <v>0.1682294678005943</v>
       </c>
       <c r="C17" t="n">
         <v>24</v>
@@ -864,13 +864,13 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1610801169128694</v>
+        <v>0.161295833393473</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1894221240993516</v>
+        <v>0.1895785534681139</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.4954760699032594</v>
+        <v>-0.4979470903702141</v>
       </c>
       <c r="H17" t="n">
         <v>24</v>
@@ -881,7 +881,7 @@
         <v>45692</v>
       </c>
       <c r="B18" t="n">
-        <v>0.1155569163438469</v>
+        <v>0.1152557755090556</v>
       </c>
       <c r="C18" t="n">
         <v>24</v>
@@ -890,13 +890,13 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1107314331125645</v>
+        <v>0.1104416666628415</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1412660416428949</v>
+        <v>0.1413198914655164</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1267063607992509</v>
+        <v>0.1260404446288963</v>
       </c>
       <c r="H18" t="n">
         <v>24</v>
@@ -907,7 +907,7 @@
         <v>45693</v>
       </c>
       <c r="B19" t="n">
-        <v>0.1549991310188867</v>
+        <v>0.1547764355598094</v>
       </c>
       <c r="C19" t="n">
         <v>24</v>
@@ -916,13 +916,13 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1484407138738746</v>
+        <v>0.148225000046646</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1977066394641253</v>
+        <v>0.1976750700626546</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.021946301433095</v>
+        <v>-1.021300632289547</v>
       </c>
       <c r="H19" t="n">
         <v>24</v>
@@ -933,7 +933,7 @@
         <v>45694</v>
       </c>
       <c r="B20" t="n">
-        <v>0.1514651359473623</v>
+        <v>0.1516916007113598</v>
       </c>
       <c r="C20" t="n">
         <v>24</v>
@@ -942,13 +942,13 @@
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1451759505008627</v>
+        <v>0.1453916667243445</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1790875089994943</v>
+        <v>0.1790622942067816</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.8692685347673739</v>
+        <v>-0.868742201012338</v>
       </c>
       <c r="H20" t="n">
         <v>24</v>
@@ -959,7 +959,7 @@
         <v>45695</v>
       </c>
       <c r="B21" t="n">
-        <v>0.1929818796168014</v>
+        <v>0.1929858169525697</v>
       </c>
       <c r="C21" t="n">
         <v>24</v>
@@ -968,13 +968,13 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1843083333042319</v>
+        <v>0.1843083333333357</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2430863728411661</v>
+        <v>0.2433501165076844</v>
       </c>
       <c r="G21" t="n">
-        <v>0.7143872009025738</v>
+        <v>0.7137670967731409</v>
       </c>
       <c r="H21" t="n">
         <v>24</v>
@@ -985,7 +985,7 @@
         <v>45696</v>
       </c>
       <c r="B22" t="n">
-        <v>0.3189483974816295</v>
+        <v>0.3187264311388228</v>
       </c>
       <c r="C22" t="n">
         <v>24</v>
@@ -994,13 +994,13 @@
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3018823830774284</v>
+        <v>0.3016666666065261</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7673348158662678</v>
+        <v>0.7672534734147926</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.6628023582655445</v>
+        <v>-0.662449841350331</v>
       </c>
       <c r="H22" t="n">
         <v>24</v>
@@ -1011,7 +1011,7 @@
         <v>45697</v>
       </c>
       <c r="B23" t="n">
-        <v>5.862482406979164</v>
+        <v>5.865113526983409</v>
       </c>
       <c r="C23" t="n">
         <v>24</v>
@@ -1020,13 +1020,13 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>3.475139034810552</v>
+        <v>3.476433333694173</v>
       </c>
       <c r="F23" t="n">
-        <v>10.66883288834785</v>
+        <v>10.66931982338762</v>
       </c>
       <c r="G23" t="n">
-        <v>0.7371351318803254</v>
+        <v>0.7371111365591267</v>
       </c>
       <c r="H23" t="n">
         <v>24</v>
@@ -1037,7 +1037,7 @@
         <v>45698</v>
       </c>
       <c r="B24" t="n">
-        <v>2.865470043448688</v>
+        <v>2.864944241437382</v>
       </c>
       <c r="C24" t="n">
         <v>24</v>
@@ -1046,13 +1046,13 @@
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>2.148313815928055</v>
+        <v>2.147883333273191</v>
       </c>
       <c r="F24" t="n">
-        <v>5.55104860241688</v>
+        <v>5.550172954718779</v>
       </c>
       <c r="G24" t="n">
-        <v>0.9167389964554694</v>
+        <v>0.916765262323759</v>
       </c>
       <c r="H24" t="n">
         <v>24</v>
@@ -1063,7 +1063,7 @@
         <v>45699</v>
       </c>
       <c r="B25" t="n">
-        <v>0.2402378207218003</v>
+        <v>0.2400114643211481</v>
       </c>
       <c r="C25" t="n">
         <v>24</v>
@@ -1072,13 +1072,13 @@
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2254740497537971</v>
+        <v>0.2252583332731935</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3666117311464869</v>
+        <v>0.3662633284455543</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.06939018670336106</v>
+        <v>-0.06735860199813448</v>
       </c>
       <c r="H25" t="n">
         <v>24</v>
@@ -1089,7 +1089,7 @@
         <v>45700</v>
       </c>
       <c r="B26" t="n">
-        <v>0.1668781835813145</v>
+        <v>0.1673393857408269</v>
       </c>
       <c r="C26" t="n">
         <v>24</v>
@@ -1098,13 +1098,13 @@
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1572769004924061</v>
+        <v>0.1577083334536133</v>
       </c>
       <c r="F26" t="n">
-        <v>0.2067045763360267</v>
+        <v>0.2066253190989311</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.0901226763502323</v>
+        <v>-0.08928685985645313</v>
       </c>
       <c r="H26" t="n">
         <v>24</v>
@@ -1115,7 +1115,7 @@
         <v>45701</v>
       </c>
       <c r="B27" t="n">
-        <v>0.1161726217924023</v>
+        <v>0.1161741662799719</v>
       </c>
       <c r="C27" t="n">
         <v>24</v>
@@ -1127,10 +1127,10 @@
         <v>0.1095250000000032</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1277626769079172</v>
+        <v>0.1276484356297941</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.3489006354850288</v>
+        <v>-0.3464894268176051</v>
       </c>
       <c r="H27" t="n">
         <v>24</v>
@@ -1141,7 +1141,7 @@
         <v>45702</v>
       </c>
       <c r="B28" t="n">
-        <v>0.361840633711621</v>
+        <v>0.3620777727390532</v>
       </c>
       <c r="C28" t="n">
         <v>24</v>
@@ -1150,13 +1150,13 @@
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>0.3371119502462054</v>
+        <v>0.337327666726809</v>
       </c>
       <c r="F28" t="n">
-        <v>0.6579448986962251</v>
+        <v>0.6580835169566702</v>
       </c>
       <c r="G28" t="n">
-        <v>0.3364093505582987</v>
+        <v>0.3361297056469769</v>
       </c>
       <c r="H28" t="n">
         <v>24</v>
@@ -1167,7 +1167,7 @@
         <v>45703</v>
       </c>
       <c r="B29" t="n">
-        <v>0.07107427971183235</v>
+        <v>0.07084480950939435</v>
       </c>
       <c r="C29" t="n">
         <v>24</v>
@@ -1176,13 +1176,13 @@
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>0.06634188308712829</v>
+        <v>0.06612616660652471</v>
       </c>
       <c r="F29" t="n">
-        <v>0.08836350131140537</v>
+        <v>0.08849510921150987</v>
       </c>
       <c r="G29" t="n">
-        <v>0.09776684451298212</v>
+        <v>0.09507728524481918</v>
       </c>
       <c r="H29" t="n">
         <v>24</v>
@@ -1193,7 +1193,7 @@
         <v>45704</v>
       </c>
       <c r="B30" t="n">
-        <v>0.1320842291288447</v>
+        <v>0.1311630474181683</v>
       </c>
       <c r="C30" t="n">
         <v>24</v>
@@ -1202,13 +1202,13 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>0.123490699015185</v>
+        <v>0.1226278330927707</v>
       </c>
       <c r="F30" t="n">
-        <v>0.1440934947264226</v>
+        <v>0.1439071916650078</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.0783417518193632</v>
+        <v>-0.07555510977072233</v>
       </c>
       <c r="H30" t="n">
         <v>24</v>
@@ -1219,7 +1219,7 @@
         <v>45705</v>
       </c>
       <c r="B31" t="n">
-        <v>0.007317953799599742</v>
+        <v>0.004555178221486922</v>
       </c>
       <c r="C31" t="n">
         <v>24</v>
@@ -1228,13 +1228,13 @@
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>0.006856597045559336</v>
+        <v>0.004267999278316263</v>
       </c>
       <c r="F31" t="n">
-        <v>0.006856597045559336</v>
+        <v>0.004267999278316262</v>
       </c>
       <c r="G31" t="n">
-        <v>0.9724530813256211</v>
+        <v>0.9893265591646878</v>
       </c>
       <c r="H31" t="n">
         <v>24</v>
@@ -1245,7 +1245,7 @@
         <v>45706</v>
       </c>
       <c r="B32" t="n">
-        <v>0.1461870494859942</v>
+        <v>0.1466494735495411</v>
       </c>
       <c r="C32" t="n">
         <v>24</v>
@@ -1254,13 +1254,13 @@
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>0.13696023382574</v>
+        <v>0.1373916667869472</v>
       </c>
       <c r="F32" t="n">
-        <v>0.1689260490128791</v>
+        <v>0.16904562011422</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.6237078004158547</v>
+        <v>-0.6260072355031556</v>
       </c>
       <c r="H32" t="n">
         <v>24</v>
@@ -1271,7 +1271,7 @@
         <v>45707</v>
       </c>
       <c r="B33" t="n">
-        <v>0.2817215140470052</v>
+        <v>0.2817211314803789</v>
       </c>
       <c r="C33" t="n">
         <v>24</v>
@@ -1283,10 +1283,10 @@
         <v>0.2700708333333329</v>
       </c>
       <c r="F33" t="n">
-        <v>0.5444385455493899</v>
+        <v>0.543949598097258</v>
       </c>
       <c r="G33" t="n">
-        <v>0.7652927321229239</v>
+        <v>0.7657141129753632</v>
       </c>
       <c r="H33" t="n">
         <v>24</v>
@@ -1297,7 +1297,7 @@
         <v>45708</v>
       </c>
       <c r="B34" t="n">
-        <v>0.1285167662130046</v>
+        <v>0.1285190553453263</v>
       </c>
       <c r="C34" t="n">
         <v>24</v>
@@ -1309,10 +1309,10 @@
         <v>0.1232124999999975</v>
       </c>
       <c r="F34" t="n">
-        <v>0.1481997572249236</v>
+        <v>0.1484189776836599</v>
       </c>
       <c r="G34" t="n">
-        <v>0.5760089588542229</v>
+        <v>0.5747536766956036</v>
       </c>
       <c r="H34" t="n">
         <v>24</v>
@@ -1323,7 +1323,7 @@
         <v>45709</v>
       </c>
       <c r="B35" t="n">
-        <v>0.157637254532524</v>
+        <v>0.1578571474486418</v>
       </c>
       <c r="C35" t="n">
         <v>24</v>
@@ -1332,13 +1332,13 @@
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>0.1506208333333324</v>
+        <v>0.150829166726807</v>
       </c>
       <c r="F35" t="n">
-        <v>0.1847912544209572</v>
+        <v>0.1849014411244309</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.573809566254593</v>
+        <v>-0.5756869774943114</v>
       </c>
       <c r="H35" t="n">
         <v>24</v>
@@ -1349,7 +1349,7 @@
         <v>45710</v>
       </c>
       <c r="B36" t="n">
-        <v>0.2249257865819405</v>
+        <v>0.2251531844037445</v>
       </c>
       <c r="C36" t="n">
         <v>24</v>
@@ -1358,13 +1358,13 @@
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>0.215780116912871</v>
+        <v>0.2159958333934746</v>
       </c>
       <c r="F36" t="n">
-        <v>0.3078340906212393</v>
+        <v>0.30765087147679</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.1539120912801801</v>
+        <v>-0.1525389108845354</v>
       </c>
       <c r="H36" t="n">
         <v>24</v>
@@ -1375,7 +1375,7 @@
         <v>45711</v>
       </c>
       <c r="B37" t="n">
-        <v>2.656264161071295</v>
+        <v>2.65653934040734</v>
       </c>
       <c r="C37" t="n">
         <v>24</v>
@@ -1384,13 +1384,13 @@
         <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>2.216084283579537</v>
+        <v>2.216300000060141</v>
       </c>
       <c r="F37" t="n">
-        <v>5.225588822266563</v>
+        <v>5.225608237350632</v>
       </c>
       <c r="G37" t="n">
-        <v>0.5557878068631963</v>
+        <v>0.5557845060167694</v>
       </c>
       <c r="H37" t="n">
         <v>24</v>
@@ -1401,7 +1401,7 @@
         <v>45712</v>
       </c>
       <c r="B38" t="n">
-        <v>0.3370366643594369</v>
+        <v>0.336591195439681</v>
       </c>
       <c r="C38" t="n">
         <v>24</v>
@@ -1410,13 +1410,13 @@
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>0.320706432840927</v>
+        <v>0.3202749998797199</v>
       </c>
       <c r="F38" t="n">
-        <v>0.5234827452452406</v>
+        <v>0.5233157722189757</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.07711144483758181</v>
+        <v>-0.07642443126762477</v>
       </c>
       <c r="H38" t="n">
         <v>24</v>
@@ -1427,7 +1427,7 @@
         <v>45713</v>
       </c>
       <c r="B39" t="n">
-        <v>0.2825902184941161</v>
+        <v>0.2833397966920618</v>
       </c>
       <c r="C39" t="n">
         <v>24</v>
@@ -1436,13 +1436,13 @@
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>0.2702028507386108</v>
+        <v>0.2709166669072284</v>
       </c>
       <c r="F39" t="n">
-        <v>0.4078308093752918</v>
+        <v>0.4078487761077886</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.9375403220119809</v>
+        <v>-0.9377110400384834</v>
       </c>
       <c r="H39" t="n">
         <v>24</v>
@@ -1453,7 +1453,7 @@
         <v>45714</v>
       </c>
       <c r="B40" t="n">
-        <v>0.1813045435242669</v>
+        <v>0.1810833610458345</v>
       </c>
       <c r="C40" t="n">
         <v>24</v>
@@ -1462,13 +1462,13 @@
         <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>0.1741948830871317</v>
+        <v>0.1739791666065281</v>
       </c>
       <c r="F40" t="n">
-        <v>0.2313111459420268</v>
+        <v>0.2313673909444823</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.7156197173694538</v>
+        <v>-0.7164541498526882</v>
       </c>
       <c r="H40" t="n">
         <v>24</v>
@@ -1479,7 +1479,7 @@
         <v>45715</v>
       </c>
       <c r="B41" t="n">
-        <v>0.2031146513260032</v>
+        <v>0.2037930624334398</v>
       </c>
       <c r="C41" t="n">
         <v>24</v>
@@ -1488,13 +1488,13 @@
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>0.1944403507386081</v>
+        <v>0.1950875001804189</v>
       </c>
       <c r="F41" t="n">
-        <v>0.249684833367164</v>
+        <v>0.2499121387945386</v>
       </c>
       <c r="G41" t="n">
-        <v>0.2076690824613494</v>
+        <v>0.2062257981843277</v>
       </c>
       <c r="H41" t="n">
         <v>24</v>
@@ -1505,7 +1505,7 @@
         <v>45716</v>
       </c>
       <c r="B42" t="n">
-        <v>2.64861163258336</v>
+        <v>2.647760380224817</v>
       </c>
       <c r="C42" t="n">
         <v>24</v>
@@ -1514,13 +1514,13 @@
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>3.153946199015187</v>
+        <v>3.153083333092773</v>
       </c>
       <c r="F42" t="n">
-        <v>6.450881143361274</v>
+        <v>6.450563883984152</v>
       </c>
       <c r="G42" t="n">
-        <v>0.8071750425135509</v>
+        <v>0.8071940086114268</v>
       </c>
       <c r="H42" t="n">
         <v>24</v>
@@ -1531,7 +1531,7 @@
         <v>45717</v>
       </c>
       <c r="B43" t="n">
-        <v>0.8066721121383511</v>
+        <v>0.8065072859619082</v>
       </c>
       <c r="C43" t="n">
         <v>24</v>
@@ -1540,13 +1540,13 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>1.021861549753802</v>
+        <v>1.021645833273199</v>
       </c>
       <c r="F43" t="n">
-        <v>1.961031665501429</v>
+        <v>1.960039235619275</v>
       </c>
       <c r="G43" t="n">
-        <v>0.937644853160873</v>
+        <v>0.9377079500025586</v>
       </c>
       <c r="H43" t="n">
         <v>24</v>
@@ -1557,7 +1557,7 @@
         <v>45718</v>
       </c>
       <c r="B44" t="n">
-        <v>0.1790029030583881</v>
+        <v>0.178787636144849</v>
       </c>
       <c r="C44" t="n">
         <v>24</v>
@@ -1566,13 +1566,13 @@
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>0.2399147661742577</v>
+        <v>0.2396249999398575</v>
       </c>
       <c r="F44" t="n">
-        <v>0.4418660610749071</v>
+        <v>0.4415098620047797</v>
       </c>
       <c r="G44" t="n">
-        <v>-5.489804919120322</v>
+        <v>-5.479345954573618</v>
       </c>
       <c r="H44" t="n">
         <v>24</v>
@@ -1583,7 +1583,7 @@
         <v>45719</v>
       </c>
       <c r="B45" t="n">
-        <v>0.3158354491580593</v>
+        <v>0.3160022392732735</v>
       </c>
       <c r="C45" t="n">
         <v>24</v>
@@ -1592,13 +1592,13 @@
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>0.4083759502461994</v>
+        <v>0.408591666726803</v>
       </c>
       <c r="F45" t="n">
-        <v>1.146417459531489</v>
+        <v>1.14698657011859</v>
       </c>
       <c r="G45" t="n">
-        <v>0.8139125202816975</v>
+        <v>0.8137277173711128</v>
       </c>
       <c r="H45" t="n">
         <v>24</v>
@@ -1609,7 +1609,7 @@
         <v>45720</v>
       </c>
       <c r="B46" t="n">
-        <v>0.4008323877948493</v>
+        <v>0.4004935203408689</v>
       </c>
       <c r="C46" t="n">
         <v>24</v>
@@ -1618,13 +1618,13 @@
         <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>0.49155226617426</v>
+        <v>0.4911208332130528</v>
       </c>
       <c r="F46" t="n">
-        <v>1.159083846031733</v>
+        <v>1.159795853104691</v>
       </c>
       <c r="G46" t="n">
-        <v>0.8863427742699107</v>
+        <v>0.886203095670656</v>
       </c>
       <c r="H46" t="n">
         <v>24</v>
@@ -1635,7 +1635,7 @@
         <v>45721</v>
       </c>
       <c r="B47" t="n">
-        <v>0.1779328413551803</v>
+        <v>0.178294736661153</v>
       </c>
       <c r="C47" t="n">
         <v>24</v>
@@ -1644,13 +1644,13 @@
         <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>0.2131977338257371</v>
+        <v>0.2136291667869443</v>
       </c>
       <c r="F47" t="n">
-        <v>0.2562459149365386</v>
+        <v>0.2566121190387541</v>
       </c>
       <c r="G47" t="n">
-        <v>0.2508070768824853</v>
+        <v>0.24866418562373</v>
       </c>
       <c r="H47" t="n">
         <v>24</v>
@@ -1661,7 +1661,7 @@
         <v>45722</v>
       </c>
       <c r="B48" t="n">
-        <v>0.1810363822210462</v>
+        <v>0.1812195288707588</v>
       </c>
       <c r="C48" t="n">
         <v>24</v>
@@ -1670,13 +1670,13 @@
         <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>0.2165092835795347</v>
+        <v>0.2167250000601383</v>
       </c>
       <c r="F48" t="n">
-        <v>0.2549029979880768</v>
+        <v>0.2545779660320834</v>
       </c>
       <c r="G48" t="n">
-        <v>0.01849197351614151</v>
+        <v>0.02099345902889438</v>
       </c>
       <c r="H48" t="n">
         <v>24</v>
@@ -1687,7 +1687,7 @@
         <v>45723</v>
       </c>
       <c r="B49" t="n">
-        <v>0.1422944462690401</v>
+        <v>0.1426548903899104</v>
       </c>
       <c r="C49" t="n">
         <v>24</v>
@@ -1696,13 +1696,13 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>0.1712352338257439</v>
+        <v>0.1716666667869511</v>
       </c>
       <c r="F49" t="n">
-        <v>0.207141646129146</v>
+        <v>0.207012127229901</v>
       </c>
       <c r="G49" t="n">
-        <v>0.02609429932488805</v>
+        <v>0.02731182135697685</v>
       </c>
       <c r="H49" t="n">
         <v>24</v>
@@ -1713,7 +1713,7 @@
         <v>45724</v>
       </c>
       <c r="B50" t="n">
-        <v>0.2194571440680035</v>
+        <v>0.219279509769354</v>
       </c>
       <c r="C50" t="n">
         <v>24</v>
@@ -1722,13 +1722,13 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>0.2632407164204646</v>
+        <v>0.263024999939861</v>
       </c>
       <c r="F50" t="n">
-        <v>0.346004388578976</v>
+        <v>0.3460975621408592</v>
       </c>
       <c r="G50" t="n">
-        <v>-0.4120833006941278</v>
+        <v>-0.4128439069168095</v>
       </c>
       <c r="H50" t="n">
         <v>24</v>
@@ -1739,7 +1739,7 @@
         <v>45725</v>
       </c>
       <c r="B51" t="n">
-        <v>0.1472186131833179</v>
+        <v>0.1470394123450915</v>
       </c>
       <c r="C51" t="n">
         <v>24</v>
@@ -1748,13 +1748,13 @@
         <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>0.1762948830871286</v>
+        <v>0.176079166606525</v>
       </c>
       <c r="F51" t="n">
-        <v>0.2280631514649246</v>
+        <v>0.2281760769659339</v>
       </c>
       <c r="G51" t="n">
-        <v>-0.2735079698884424</v>
+        <v>-0.2747694374141108</v>
       </c>
       <c r="H51" t="n">
         <v>24</v>
@@ -1765,7 +1765,7 @@
         <v>45726</v>
       </c>
       <c r="B52" t="n">
-        <v>0.1485796797868249</v>
+        <v>0.1487615581434885</v>
       </c>
       <c r="C52" t="n">
         <v>24</v>
@@ -1774,13 +1774,13 @@
         <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>0.177996783579534</v>
+        <v>0.1782125000601376</v>
       </c>
       <c r="F52" t="n">
-        <v>0.2247820189152352</v>
+        <v>0.2247371195706378</v>
       </c>
       <c r="G52" t="n">
-        <v>-1.178035645233388</v>
+        <v>-1.177165623630884</v>
       </c>
       <c r="H52" t="n">
         <v>24</v>
@@ -1791,7 +1791,7 @@
         <v>45727</v>
       </c>
       <c r="B53" t="n">
-        <v>0.2107608966903169</v>
+        <v>0.2107082224579345</v>
       </c>
       <c r="C53" t="n">
         <v>24</v>
@@ -1800,13 +1800,13 @@
         <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>0.2523823830871308</v>
+        <v>0.2523166667268093</v>
       </c>
       <c r="F53" t="n">
-        <v>0.3189505739121738</v>
+        <v>0.3189321557927244</v>
       </c>
       <c r="G53" t="n">
-        <v>-0.8254086736091781</v>
+        <v>-0.8251978596021381</v>
       </c>
       <c r="H53" t="n">
         <v>24</v>
@@ -1817,7 +1817,7 @@
         <v>45728</v>
       </c>
       <c r="B54" t="n">
-        <v>4.82145155794937</v>
+        <v>4.821719824739232</v>
       </c>
       <c r="C54" t="n">
         <v>24</v>
@@ -1826,13 +1826,13 @@
         <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>5.128709283579535</v>
+        <v>5.128925000060138</v>
       </c>
       <c r="F54" t="n">
-        <v>9.927852394894142</v>
+        <v>9.927852600627928</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.1212197246112976</v>
+        <v>-0.1212197710811225</v>
       </c>
       <c r="H54" t="n">
         <v>24</v>
@@ -1843,7 +1843,7 @@
         <v>45729</v>
       </c>
       <c r="B55" t="n">
-        <v>0.7343881162749384</v>
+        <v>0.7343777834640847</v>
       </c>
       <c r="C55" t="n">
         <v>24</v>
@@ -1852,13 +1852,13 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>0.7990000000194014</v>
+        <v>0.7990000000024242</v>
       </c>
       <c r="F55" t="n">
-        <v>2.871143922863889</v>
+        <v>2.871676839095814</v>
       </c>
       <c r="G55" t="n">
-        <v>0.7480562577569247</v>
+        <v>0.7479627219580163</v>
       </c>
       <c r="H55" t="n">
         <v>24</v>
@@ -1869,7 +1869,7 @@
         <v>45730</v>
       </c>
       <c r="B56" t="n">
-        <v>0.5368391375218725</v>
+        <v>0.5360892684071833</v>
       </c>
       <c r="C56" t="n">
         <v>24</v>
@@ -1878,13 +1878,13 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>0.6109045327680965</v>
+        <v>0.6100416665526733</v>
       </c>
       <c r="F56" t="n">
-        <v>1.452660725838274</v>
+        <v>1.451740962774442</v>
       </c>
       <c r="G56" t="n">
-        <v>0.9316435258656779</v>
+        <v>0.9317300592937534</v>
       </c>
       <c r="H56" t="n">
         <v>24</v>
@@ -1895,7 +1895,7 @@
         <v>45731</v>
       </c>
       <c r="B57" t="n">
-        <v>0.1556070899421053</v>
+        <v>0.1557916662689601</v>
       </c>
       <c r="C57" t="n">
         <v>24</v>
@@ -1904,13 +1904,13 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>0.1833551168352555</v>
+        <v>0.1835708334226111</v>
       </c>
       <c r="F57" t="n">
-        <v>0.2193681004806682</v>
+        <v>0.219559592403693</v>
       </c>
       <c r="G57" t="n">
-        <v>-0.96894840450397</v>
+        <v>-0.9723873938404632</v>
       </c>
       <c r="H57" t="n">
         <v>24</v>
@@ -1921,7 +1921,7 @@
         <v>45732</v>
       </c>
       <c r="B58" t="n">
-        <v>1.314423207749475</v>
+        <v>1.31443107522064</v>
       </c>
       <c r="C58" t="n">
         <v>24</v>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="E58" t="n">
-        <v>1.502279166489618</v>
+        <v>1.50227916675106</v>
       </c>
       <c r="F58" t="n">
-        <v>3.24198494724033</v>
+        <v>3.241942713101215</v>
       </c>
       <c r="G58" t="n">
-        <v>-0.2118301427741247</v>
+        <v>-0.2117985693582725</v>
       </c>
       <c r="H58" t="n">
         <v>24</v>
@@ -1947,7 +1947,7 @@
         <v>45733</v>
       </c>
       <c r="B59" t="n">
-        <v>1.168958614452935</v>
+        <v>1.169798519625096</v>
       </c>
       <c r="C59" t="n">
         <v>24</v>
@@ -1956,13 +1956,13 @@
         <v>0</v>
       </c>
       <c r="E59" t="n">
-        <v>1.127212134293893</v>
+        <v>1.128075000208577</v>
       </c>
       <c r="F59" t="n">
-        <v>4.654172682072267</v>
+        <v>4.654734818927892</v>
       </c>
       <c r="G59" t="n">
-        <v>0.801703356273359</v>
+        <v>0.8016554523423554</v>
       </c>
       <c r="H59" t="n">
         <v>24</v>
@@ -1973,7 +1973,7 @@
         <v>45734</v>
       </c>
       <c r="B60" t="n">
-        <v>1.05450089186873</v>
+        <v>1.054321845871975</v>
       </c>
       <c r="C60" t="n">
         <v>24</v>
@@ -1982,13 +1982,13 @@
         <v>0</v>
       </c>
       <c r="E60" t="n">
-        <v>1.229761549753798</v>
+        <v>1.229545833333335</v>
       </c>
       <c r="F60" t="n">
-        <v>4.640442604989145</v>
+        <v>4.639849804022194</v>
       </c>
       <c r="G60" t="n">
-        <v>0.8451896704491175</v>
+        <v>0.8452292209226818</v>
       </c>
       <c r="H60" t="n">
         <v>24</v>
@@ -1999,7 +1999,7 @@
         <v>45735</v>
       </c>
       <c r="B61" t="n">
-        <v>0.6313222698865903</v>
+        <v>0.6315206889837534</v>
       </c>
       <c r="C61" t="n">
         <v>24</v>
@@ -2008,13 +2008,13 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>0.7071759502195221</v>
+        <v>0.7073916667243031</v>
       </c>
       <c r="F61" t="n">
-        <v>1.917711814649294</v>
+        <v>1.918466581520136</v>
       </c>
       <c r="G61" t="n">
-        <v>0.6070362374766065</v>
+        <v>0.6067268537686004</v>
       </c>
       <c r="H61" t="n">
         <v>24</v>
@@ -2025,7 +2025,7 @@
         <v>45736</v>
       </c>
       <c r="B62" t="n">
-        <v>0.1847147891293828</v>
+        <v>0.1849193381527482</v>
       </c>
       <c r="C62" t="n">
         <v>24</v>
@@ -2034,13 +2034,13 @@
         <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>0.1974217980223128</v>
+        <v>0.1976375047104248</v>
       </c>
       <c r="F62" t="n">
-        <v>0.2230057664380618</v>
+        <v>0.2229592489776799</v>
       </c>
       <c r="G62" t="n">
-        <v>-0.5867473015717295</v>
+        <v>-0.5860854015891741</v>
       </c>
       <c r="H62" t="n">
         <v>24</v>
@@ -2051,7 +2051,7 @@
         <v>45737</v>
       </c>
       <c r="B63" t="n">
-        <v>0.7996452025905996</v>
+        <v>0.8000884548339671</v>
       </c>
       <c r="C63" t="n">
         <v>24</v>
@@ -2060,13 +2060,13 @@
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>0.7648685664824093</v>
+        <v>0.7652999997259009</v>
       </c>
       <c r="F63" t="n">
-        <v>2.41061340209948</v>
+        <v>2.411142689798054</v>
       </c>
       <c r="G63" t="n">
-        <v>0.8045259477824345</v>
+        <v>0.8044400996165804</v>
       </c>
       <c r="H63" t="n">
         <v>24</v>
@@ -2077,7 +2077,7 @@
         <v>45738</v>
       </c>
       <c r="B64" t="n">
-        <v>0.619434218773159</v>
+        <v>0.6189796968320547</v>
       </c>
       <c r="C64" t="n">
         <v>24</v>
@@ -2086,13 +2086,13 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>0.642993932903984</v>
+        <v>0.6425624998578906</v>
       </c>
       <c r="F64" t="n">
-        <v>1.764734573453674</v>
+        <v>1.76391844015623</v>
       </c>
       <c r="G64" t="n">
-        <v>0.8429504524836713</v>
+        <v>0.8430956796798323</v>
       </c>
       <c r="H64" t="n">
         <v>24</v>
@@ -2103,7 +2103,7 @@
         <v>45739</v>
       </c>
       <c r="B65" t="n">
-        <v>2.084309519444218</v>
+        <v>2.084153717469959</v>
       </c>
       <c r="C65" t="n">
         <v>24</v>
@@ -2112,13 +2112,13 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>2.464674049790178</v>
+        <v>2.464458333263001</v>
       </c>
       <c r="F65" t="n">
-        <v>3.998178181266816</v>
+        <v>3.997438486913246</v>
       </c>
       <c r="G65" t="n">
-        <v>0.8825033011980776</v>
+        <v>0.8825467727999216</v>
       </c>
       <c r="H65" t="n">
         <v>24</v>
@@ -2129,7 +2129,7 @@
         <v>45740</v>
       </c>
       <c r="B66" t="n">
-        <v>0.8334651816582936</v>
+        <v>0.8334790373059167</v>
       </c>
       <c r="C66" t="n">
         <v>24</v>
@@ -2138,13 +2138,13 @@
         <v>0</v>
       </c>
       <c r="E66" t="n">
-        <v>1.018691666664239</v>
+        <v>1.018691666666664</v>
       </c>
       <c r="F66" t="n">
-        <v>2.393409112214111</v>
+        <v>2.394364470399276</v>
       </c>
       <c r="G66" t="n">
-        <v>0.9349645053906723</v>
+        <v>0.9349125756205449</v>
       </c>
       <c r="H66" t="n">
         <v>24</v>
@@ -2155,7 +2155,7 @@
         <v>45741</v>
       </c>
       <c r="B67" t="n">
-        <v>0.8200539010747548</v>
+        <v>0.8204401421705483</v>
       </c>
       <c r="C67" t="n">
         <v>24</v>
@@ -2164,13 +2164,13 @@
         <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>0.9040144004924038</v>
+        <v>0.9044458334531184</v>
       </c>
       <c r="F67" t="n">
-        <v>2.761523219569606</v>
+        <v>2.761535610023544</v>
       </c>
       <c r="G67" t="n">
-        <v>-1.081591928019139</v>
+        <v>-1.081610607512095</v>
       </c>
       <c r="H67" t="n">
         <v>24</v>
@@ -2181,7 +2181,7 @@
         <v>45742</v>
       </c>
       <c r="B68" t="n">
-        <v>0.1311712861239799</v>
+        <v>0.1306757271066566</v>
       </c>
       <c r="C68" t="n">
         <v>24</v>
@@ -2190,13 +2190,13 @@
         <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>0.1508804825947247</v>
+        <v>0.1503083332130532</v>
       </c>
       <c r="F68" t="n">
-        <v>0.1957515412738579</v>
+        <v>0.1953455526947083</v>
       </c>
       <c r="G68" t="n">
-        <v>-0.1033052609865608</v>
+        <v>-0.0987334979263268</v>
       </c>
       <c r="H68" t="n">
         <v>24</v>
@@ -2207,7 +2207,7 @@
         <v>45743</v>
       </c>
       <c r="B69" t="n">
-        <v>0.8525867602624643</v>
+        <v>0.8525958854456912</v>
       </c>
       <c r="C69" t="n">
         <v>24</v>
@@ -2216,13 +2216,13 @@
         <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>0.9414374997089574</v>
+        <v>0.9414374999703993</v>
       </c>
       <c r="F69" t="n">
-        <v>2.760802912267711</v>
+        <v>2.760816806147507</v>
       </c>
       <c r="G69" t="n">
-        <v>-0.9701681433105569</v>
+        <v>-0.9701879733014036</v>
       </c>
       <c r="H69" t="n">
         <v>24</v>
@@ -2233,7 +2233,7 @@
         <v>45744</v>
       </c>
       <c r="B70" t="n">
-        <v>0.833697268072899</v>
+        <v>0.8333314732426175</v>
       </c>
       <c r="C70" t="n">
         <v>24</v>
@@ -2242,13 +2242,13 @@
         <v>0</v>
       </c>
       <c r="E70" t="n">
-        <v>0.9212522684952873</v>
+        <v>0.9208208335331918</v>
       </c>
       <c r="F70" t="n">
-        <v>2.818965262486597</v>
+        <v>2.818953961355986</v>
       </c>
       <c r="G70" t="n">
-        <v>-1.08561803191573</v>
+        <v>-1.085601309613507</v>
       </c>
       <c r="H70" t="n">
         <v>24</v>
@@ -2259,7 +2259,7 @@
         <v>45745</v>
       </c>
       <c r="B71" t="n">
-        <v>0.3581996297684251</v>
+        <v>0.358200894993455</v>
       </c>
       <c r="C71" t="n">
         <v>24</v>
@@ -2268,13 +2268,13 @@
         <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>0.4263083335540383</v>
+        <v>0.4263083332518587</v>
       </c>
       <c r="F71" t="n">
-        <v>0.782774152146979</v>
+        <v>0.7821387571036067</v>
       </c>
       <c r="G71" t="n">
-        <v>0.7889776925276242</v>
+        <v>0.7893201364087069</v>
       </c>
       <c r="H71" t="n">
         <v>24</v>
@@ -2285,7 +2285,7 @@
         <v>45746</v>
       </c>
       <c r="B72" t="n">
-        <v>0.1875250147350691</v>
+        <v>0.1877071314114798</v>
       </c>
       <c r="C72" t="n">
         <v>24</v>
@@ -2294,13 +2294,13 @@
         <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>0.2251551169128749</v>
+        <v>0.2253708333934785</v>
       </c>
       <c r="F72" t="n">
-        <v>0.2665007128193081</v>
+        <v>0.2664446275993527</v>
       </c>
       <c r="G72" t="n">
-        <v>-1.055532212851882</v>
+        <v>-1.054667128145947</v>
       </c>
       <c r="H72" t="n">
         <v>24</v>
@@ -2311,7 +2311,7 @@
         <v>45747</v>
       </c>
       <c r="B73" t="n">
-        <v>0.1323463137549217</v>
+        <v>0.1321681171851038</v>
       </c>
       <c r="C73" t="n">
         <v>24</v>
@@ -2320,13 +2320,13 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>0.1588532164204578</v>
+        <v>0.1586374999412564</v>
       </c>
       <c r="F73" t="n">
-        <v>0.1885523380205054</v>
+        <v>0.1884726007725817</v>
       </c>
       <c r="G73" t="n">
-        <v>-0.7086802678808752</v>
+        <v>-0.7072353995220493</v>
       </c>
       <c r="H73" t="n">
         <v>24</v>
@@ -2337,7 +2337,7 @@
         <v>45748</v>
       </c>
       <c r="B74" t="n">
-        <v>0.1476700221433787</v>
+        <v>0.1480311969511916</v>
       </c>
       <c r="C74" t="n">
         <v>24</v>
@@ -2346,13 +2346,13 @@
         <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>0.1770852338208856</v>
+        <v>0.1775166667801222</v>
       </c>
       <c r="F74" t="n">
-        <v>0.2164141659752012</v>
+        <v>0.2167029073301669</v>
       </c>
       <c r="G74" t="n">
-        <v>0.3712093029471679</v>
+        <v>0.3695303093844405</v>
       </c>
       <c r="H74" t="n">
         <v>24</v>
@@ -2363,7 +2363,7 @@
         <v>45749</v>
       </c>
       <c r="B75" t="n">
-        <v>0.1708294897900333</v>
+        <v>0.1704712908590625</v>
       </c>
       <c r="C75" t="n">
         <v>24</v>
@@ -2372,13 +2372,13 @@
         <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>0.2050772661742582</v>
+        <v>0.204645833213051</v>
       </c>
       <c r="F75" t="n">
-        <v>0.254678968218123</v>
+        <v>0.2544472202356316</v>
       </c>
       <c r="G75" t="n">
-        <v>0.1363247441552792</v>
+        <v>0.1378958509712617</v>
       </c>
       <c r="H75" t="n">
         <v>24</v>
@@ -2389,7 +2389,7 @@
         <v>45750</v>
       </c>
       <c r="B76" t="n">
-        <v>0.103993692572588</v>
+        <v>0.1036358710628074</v>
       </c>
       <c r="C76" t="n">
         <v>24</v>
@@ -2398,13 +2398,13 @@
         <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>0.1252189328409236</v>
+        <v>0.1247874998797164</v>
       </c>
       <c r="F76" t="n">
-        <v>0.1501746124639264</v>
+        <v>0.1496623935475549</v>
       </c>
       <c r="G76" t="n">
-        <v>0.6290992499899037</v>
+        <v>0.6316250881335241</v>
       </c>
       <c r="H76" t="n">
         <v>24</v>
@@ -2415,7 +2415,7 @@
         <v>45751</v>
       </c>
       <c r="B77" t="n">
-        <v>0.08799992730632156</v>
+        <v>0.08793839478903805</v>
       </c>
       <c r="C77" t="n">
         <v>24</v>
@@ -2424,13 +2424,13 @@
         <v>0</v>
       </c>
       <c r="E77" t="n">
-        <v>0.1059323830871287</v>
+        <v>0.1058583333333321</v>
       </c>
       <c r="F77" t="n">
-        <v>0.1467994026262535</v>
+        <v>0.1471643583382592</v>
       </c>
       <c r="G77" t="n">
-        <v>0.4845451471311553</v>
+        <v>0.481979032714846</v>
       </c>
       <c r="H77" t="n">
         <v>24</v>
@@ -2441,7 +2441,7 @@
         <v>45752</v>
       </c>
       <c r="B78" t="n">
-        <v>0.1507834752241965</v>
+        <v>0.1507849259828458</v>
       </c>
       <c r="C78" t="n">
         <v>24</v>
@@ -2453,10 +2453,10 @@
         <v>0.1807124999999991</v>
       </c>
       <c r="F78" t="n">
-        <v>0.216932999200871</v>
+        <v>0.2172255692913405</v>
       </c>
       <c r="G78" t="n">
-        <v>-0.02928829139064648</v>
+        <v>-0.03206649514514281</v>
       </c>
       <c r="H78" t="n">
         <v>24</v>
@@ -2467,7 +2467,7 @@
         <v>45753</v>
       </c>
       <c r="B79" t="n">
-        <v>0.3488782931608858</v>
+        <v>0.3487032841423967</v>
       </c>
       <c r="C79" t="n">
         <v>24</v>
@@ -2476,13 +2476,13 @@
         <v>0</v>
       </c>
       <c r="E79" t="n">
-        <v>0.4154615497537962</v>
+        <v>0.4152458332731926</v>
       </c>
       <c r="F79" t="n">
-        <v>0.9423194297826779</v>
+        <v>0.9422893533319427</v>
       </c>
       <c r="G79" t="n">
-        <v>-0.8366643396811158</v>
+        <v>-0.8365470981996868</v>
       </c>
       <c r="H79" t="n">
         <v>24</v>
@@ -2493,7 +2493,7 @@
         <v>45754</v>
       </c>
       <c r="B80" t="n">
-        <v>0.1094759848424613</v>
+        <v>0.1098373101888102</v>
       </c>
       <c r="C80" t="n">
         <v>24</v>
@@ -2502,13 +2502,13 @@
         <v>0</v>
       </c>
       <c r="E80" t="n">
-        <v>0.1310894004924042</v>
+        <v>0.1315208334536114</v>
       </c>
       <c r="F80" t="n">
-        <v>0.1576807006448797</v>
+        <v>0.1577785117196539</v>
       </c>
       <c r="G80" t="n">
-        <v>-0.04534286122800668</v>
+        <v>-0.04664013883445484</v>
       </c>
       <c r="H80" t="n">
         <v>24</v>
@@ -2519,7 +2519,7 @@
         <v>45755</v>
       </c>
       <c r="B81" t="n">
-        <v>0.1249720445265653</v>
+        <v>0.1251470534084059</v>
       </c>
       <c r="C81" t="n">
         <v>24</v>
@@ -2528,13 +2528,13 @@
         <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>0.1495583333333362</v>
+        <v>0.1497666667268097</v>
       </c>
       <c r="F81" t="n">
-        <v>0.1889854053117261</v>
+        <v>0.1891673421983413</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.7531430891675726</v>
+        <v>-0.7565202274975193</v>
       </c>
       <c r="H81" t="n">
         <v>24</v>
@@ -2545,7 +2545,7 @@
         <v>45756</v>
       </c>
       <c r="B82" t="n">
-        <v>0.1097252680396114</v>
+        <v>0.1097264075079529</v>
       </c>
       <c r="C82" t="n">
         <v>24</v>
@@ -2557,10 +2557,10 @@
         <v>0.1314791666666709</v>
       </c>
       <c r="F82" t="n">
-        <v>0.1755644457868919</v>
+        <v>0.1753076045890332</v>
       </c>
       <c r="G82" t="n">
-        <v>-0.4779668981770631</v>
+        <v>-0.4736456915939531</v>
       </c>
       <c r="H82" t="n">
         <v>24</v>
@@ -2571,7 +2571,7 @@
         <v>45757</v>
       </c>
       <c r="B83" t="n">
-        <v>0.1611933067372631</v>
+        <v>0.1612891231331977</v>
       </c>
       <c r="C83" t="n">
         <v>23</v>
@@ -2580,13 +2580,13 @@
         <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>0.192952669693672</v>
+        <v>0.1930652174226825</v>
       </c>
       <c r="F83" t="n">
-        <v>0.2195958934217697</v>
+        <v>0.2197731192312188</v>
       </c>
       <c r="G83" t="n">
-        <v>-0.925734720461969</v>
+        <v>-0.9288443197266538</v>
       </c>
       <c r="H83" t="n">
         <v>23</v>

--- a/optimized_version/metadata/validation_daily_metrics/agus4_validation_daily_metrics.xlsx
+++ b/optimized_version/metadata/validation_daily_metrics/agus4_validation_daily_metrics.xlsx
@@ -467,7 +467,7 @@
         <v>45676</v>
       </c>
       <c r="B2" t="n">
-        <v>0.2226321950879064</v>
+        <v>0.2226321922893521</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
@@ -476,10 +476,10 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.214200000698952</v>
+        <v>0.2141999980063929</v>
       </c>
       <c r="F2" t="n">
-        <v>0.214200000698952</v>
+        <v>0.2141999980063929</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
@@ -491,7 +491,7 @@
         <v>45677</v>
       </c>
       <c r="B3" t="n">
-        <v>3.108856290469382</v>
+        <v>3.108856290350812</v>
       </c>
       <c r="C3" t="n">
         <v>24</v>
@@ -500,13 +500,13 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>2.509379166724873</v>
+        <v>2.509379166633924</v>
       </c>
       <c r="F3" t="n">
-        <v>5.926175501856475</v>
+        <v>5.926175501849403</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2049403363076855</v>
+        <v>0.2049403363095833</v>
       </c>
       <c r="H3" t="n">
         <v>24</v>
@@ -517,7 +517,7 @@
         <v>45678</v>
       </c>
       <c r="B4" t="n">
-        <v>5.478969175895346</v>
+        <v>5.47896917591629</v>
       </c>
       <c r="C4" t="n">
         <v>24</v>
@@ -526,13 +526,13 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>3.889824999939858</v>
+        <v>3.889825000032741</v>
       </c>
       <c r="F4" t="n">
-        <v>9.388450136379054</v>
+        <v>9.38845013638378</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3991756104489157</v>
+        <v>0.399175610448311</v>
       </c>
       <c r="H4" t="n">
         <v>24</v>
@@ -543,7 +543,7 @@
         <v>45679</v>
       </c>
       <c r="B5" t="n">
-        <v>0.1381093329588311</v>
+        <v>0.1381093331671204</v>
       </c>
       <c r="C5" t="n">
         <v>24</v>
@@ -552,13 +552,13 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0.132808333153406</v>
+        <v>0.1328083333551623</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1692488872983076</v>
+        <v>0.1692488871685451</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7413866740638704</v>
+        <v>0.7413866744604259</v>
       </c>
       <c r="H5" t="n">
         <v>24</v>
@@ -569,7 +569,7 @@
         <v>45680</v>
       </c>
       <c r="B6" t="n">
-        <v>0.1440157209481648</v>
+        <v>0.1440157210441397</v>
       </c>
       <c r="C6" t="n">
         <v>24</v>
@@ -578,13 +578,13 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1383583332731906</v>
+        <v>0.1383583333660727</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1610603147308466</v>
+        <v>0.1610603148209835</v>
       </c>
       <c r="G6" t="n">
-        <v>0.04271806607822226</v>
+        <v>0.04271806500674247</v>
       </c>
       <c r="H6" t="n">
         <v>24</v>
@@ -595,7 +595,7 @@
         <v>45681</v>
       </c>
       <c r="B7" t="n">
-        <v>0.1640237582394342</v>
+        <v>0.1640237579485158</v>
       </c>
       <c r="C7" t="n">
         <v>24</v>
@@ -604,13 +604,13 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1573583335137538</v>
+        <v>0.1573583332351074</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2080286820430637</v>
+        <v>0.2080286818479041</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3951398776183513</v>
+        <v>0.3951398787532358</v>
       </c>
       <c r="H7" t="n">
         <v>24</v>
@@ -621,7 +621,7 @@
         <v>45682</v>
       </c>
       <c r="B8" t="n">
-        <v>5.108929411945848</v>
+        <v>5.108929411667181</v>
       </c>
       <c r="C8" t="n">
         <v>24</v>
@@ -630,13 +630,13 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>2.386995833393474</v>
+        <v>2.386995833300592</v>
       </c>
       <c r="F8" t="n">
-        <v>10.18844310086371</v>
+        <v>10.18844310061456</v>
       </c>
       <c r="G8" t="n">
-        <v>0.662465609057165</v>
+        <v>0.6624656090736729</v>
       </c>
       <c r="H8" t="n">
         <v>24</v>
@@ -647,7 +647,7 @@
         <v>45683</v>
       </c>
       <c r="B9" t="n">
-        <v>2.675309175210205</v>
+        <v>2.675309175275907</v>
       </c>
       <c r="C9" t="n">
         <v>24</v>
@@ -659,10 +659,10 @@
         <v>2.505262499999997</v>
       </c>
       <c r="F9" t="n">
-        <v>10.6970186627919</v>
+        <v>10.69701866303001</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05953133648391928</v>
+        <v>0.05953133644204966</v>
       </c>
       <c r="H9" t="n">
         <v>24</v>
@@ -673,7 +673,7 @@
         <v>45684</v>
       </c>
       <c r="B10" t="n">
-        <v>0.1735797290238908</v>
+        <v>0.1735797290231245</v>
       </c>
       <c r="C10" t="n">
         <v>24</v>
@@ -685,10 +685,10 @@
         <v>0.1665458333333317</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1885893411010168</v>
+        <v>0.1885893411272921</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.7982535866112124</v>
+        <v>-0.7982535871122991</v>
       </c>
       <c r="H10" t="n">
         <v>24</v>
@@ -699,7 +699,7 @@
         <v>45685</v>
       </c>
       <c r="B11" t="n">
-        <v>0.1361325518234008</v>
+        <v>0.1361325517257788</v>
       </c>
       <c r="C11" t="n">
         <v>24</v>
@@ -708,13 +708,13 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1307083333934737</v>
+        <v>0.1307083333005915</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1546655713307715</v>
+        <v>0.154665571347046</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.341860755288604</v>
+        <v>-1.341860755781443</v>
       </c>
       <c r="H11" t="n">
         <v>24</v>
@@ -725,7 +725,7 @@
         <v>45686</v>
       </c>
       <c r="B12" t="n">
-        <v>0.1973398658917872</v>
+        <v>0.1973398656004244</v>
       </c>
       <c r="C12" t="n">
         <v>24</v>
@@ -734,13 +734,13 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1894625001804234</v>
+        <v>0.189462499901777</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2130467290670871</v>
+        <v>0.2130467290084273</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.811030311812595</v>
+        <v>-1.811030310264629</v>
       </c>
       <c r="H12" t="n">
         <v>24</v>
@@ -751,7 +751,7 @@
         <v>45687</v>
       </c>
       <c r="B13" t="n">
-        <v>0.169386148730038</v>
+        <v>0.1693861487294512</v>
       </c>
       <c r="C13" t="n">
         <v>24</v>
@@ -763,10 +763,10 @@
         <v>0.162133333333335</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1964990118894634</v>
+        <v>0.1964990118624731</v>
       </c>
       <c r="G13" t="n">
-        <v>0.220103082612102</v>
+        <v>0.2201030828263489</v>
       </c>
       <c r="H13" t="n">
         <v>24</v>
@@ -777,7 +777,7 @@
         <v>45688</v>
       </c>
       <c r="B14" t="n">
-        <v>0.1579879719539322</v>
+        <v>0.1579879719529522</v>
       </c>
       <c r="C14" t="n">
         <v>24</v>
@@ -789,10 +789,10 @@
         <v>0.1513208333333325</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1724693275597243</v>
+        <v>0.1724693276019461</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.4142611941521668</v>
+        <v>-0.4142611948446102</v>
       </c>
       <c r="H14" t="n">
         <v>24</v>
@@ -803,7 +803,7 @@
         <v>45689</v>
       </c>
       <c r="B15" t="n">
-        <v>0.3541152082416876</v>
+        <v>0.3541152081430309</v>
       </c>
       <c r="C15" t="n">
         <v>24</v>
@@ -812,13 +812,13 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3384166667268046</v>
+        <v>0.3384166666339225</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6610977045942947</v>
+        <v>0.6610977045711127</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.242431157423919</v>
+        <v>-1.242431157266652</v>
       </c>
       <c r="H15" t="n">
         <v>24</v>
@@ -829,7 +829,7 @@
         <v>45690</v>
       </c>
       <c r="B16" t="n">
-        <v>8.085327723082161</v>
+        <v>8.085327723311837</v>
       </c>
       <c r="C16" t="n">
         <v>24</v>
@@ -838,13 +838,13 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>4.700662499819583</v>
+        <v>4.70066250009823</v>
       </c>
       <c r="F16" t="n">
-        <v>11.3138482373548</v>
+        <v>11.31384823735619</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4852254833113474</v>
+        <v>0.4852254833112217</v>
       </c>
       <c r="H16" t="n">
         <v>24</v>
@@ -855,7 +855,7 @@
         <v>45691</v>
       </c>
       <c r="B17" t="n">
-        <v>0.1682294678005943</v>
+        <v>0.1682294677029387</v>
       </c>
       <c r="C17" t="n">
         <v>24</v>
@@ -864,13 +864,13 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>0.161295833393473</v>
+        <v>0.1612958333005909</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1895785534681139</v>
+        <v>0.1895785533931776</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.4979470903702141</v>
+        <v>-0.4979470891860012</v>
       </c>
       <c r="H17" t="n">
         <v>24</v>
@@ -881,7 +881,7 @@
         <v>45692</v>
       </c>
       <c r="B18" t="n">
-        <v>0.1152557755090556</v>
+        <v>0.1152557761292788</v>
       </c>
       <c r="C18" t="n">
         <v>24</v>
@@ -890,13 +890,13 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1104416666628415</v>
+        <v>0.1104416672560215</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1413198914655164</v>
+        <v>0.141319891268715</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1260404446288963</v>
+        <v>0.1260404470630394</v>
       </c>
       <c r="H18" t="n">
         <v>24</v>
@@ -907,7 +907,7 @@
         <v>45693</v>
       </c>
       <c r="B19" t="n">
-        <v>0.1547764355598094</v>
+        <v>0.1547764338267132</v>
       </c>
       <c r="C19" t="n">
         <v>24</v>
@@ -916,13 +916,13 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>0.148225000046646</v>
+        <v>0.1482249983786706</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1976750700626546</v>
+        <v>0.1976750700986945</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.021300632289547</v>
+        <v>-1.02130063302659</v>
       </c>
       <c r="H19" t="n">
         <v>24</v>
@@ -933,7 +933,7 @@
         <v>45694</v>
       </c>
       <c r="B20" t="n">
-        <v>0.1516916007113598</v>
+        <v>0.1516916007316317</v>
       </c>
       <c r="C20" t="n">
         <v>24</v>
@@ -942,13 +942,13 @@
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1453916667243445</v>
+        <v>0.1453916667442776</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1790622942067816</v>
+        <v>0.1790622943383895</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.868742201012338</v>
+        <v>-0.86874220375933</v>
       </c>
       <c r="H20" t="n">
         <v>24</v>
@@ -959,7 +959,7 @@
         <v>45695</v>
       </c>
       <c r="B21" t="n">
-        <v>0.1929858169525697</v>
+        <v>0.1929858169266957</v>
       </c>
       <c r="C21" t="n">
         <v>24</v>
@@ -968,13 +968,13 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1843083333333357</v>
+        <v>0.1843083333102952</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2433501165076844</v>
+        <v>0.2433501163869971</v>
       </c>
       <c r="G21" t="n">
-        <v>0.7137670967731409</v>
+        <v>0.71376709705705</v>
       </c>
       <c r="H21" t="n">
         <v>24</v>
@@ -985,7 +985,7 @@
         <v>45696</v>
       </c>
       <c r="B22" t="n">
-        <v>0.3187264311388228</v>
+        <v>0.3187265767070852</v>
       </c>
       <c r="C22" t="n">
         <v>24</v>
@@ -994,13 +994,13 @@
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3016666666065261</v>
+        <v>0.3016668057077911</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7672534734147926</v>
+        <v>0.7672534967809924</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.662449841350331</v>
+        <v>-0.6624499426079653</v>
       </c>
       <c r="H22" t="n">
         <v>24</v>
@@ -1011,7 +1011,7 @@
         <v>45697</v>
       </c>
       <c r="B23" t="n">
-        <v>5.865113526983409</v>
+        <v>5.865113525850513</v>
       </c>
       <c r="C23" t="n">
         <v>24</v>
@@ -1020,13 +1020,13 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>3.476433333694173</v>
+        <v>3.47643333313688</v>
       </c>
       <c r="F23" t="n">
-        <v>10.66931982338762</v>
+        <v>10.66931982317782</v>
       </c>
       <c r="G23" t="n">
-        <v>0.7371111365591267</v>
+        <v>0.7371111365694651</v>
       </c>
       <c r="H23" t="n">
         <v>24</v>
@@ -1037,7 +1037,7 @@
         <v>45698</v>
       </c>
       <c r="B24" t="n">
-        <v>2.864944241437382</v>
+        <v>2.864944241467375</v>
       </c>
       <c r="C24" t="n">
         <v>24</v>
@@ -1046,13 +1046,13 @@
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>2.147883333273191</v>
+        <v>2.147883333366074</v>
       </c>
       <c r="F24" t="n">
-        <v>5.550172954718779</v>
+        <v>5.550172955095581</v>
       </c>
       <c r="G24" t="n">
-        <v>0.916765262323759</v>
+        <v>0.9167652623124574</v>
       </c>
       <c r="H24" t="n">
         <v>24</v>
@@ -1063,7 +1063,7 @@
         <v>45699</v>
       </c>
       <c r="B25" t="n">
-        <v>0.2400114643211481</v>
+        <v>0.2400114644186115</v>
       </c>
       <c r="C25" t="n">
         <v>24</v>
@@ -1072,13 +1072,13 @@
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2252583332731935</v>
+        <v>0.2252583333660757</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3662633284455543</v>
+        <v>0.3662633285917005</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.06735860199813448</v>
+        <v>-0.06735860284992801</v>
       </c>
       <c r="H25" t="n">
         <v>24</v>
@@ -1089,7 +1089,7 @@
         <v>45700</v>
       </c>
       <c r="B26" t="n">
-        <v>0.1673393857408269</v>
+        <v>0.1673393855422447</v>
       </c>
       <c r="C26" t="n">
         <v>24</v>
@@ -1098,13 +1098,13 @@
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1577083334536133</v>
+        <v>0.157708333267849</v>
       </c>
       <c r="F26" t="n">
-        <v>0.2066253190989311</v>
+        <v>0.2066253191260821</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.08928685985645313</v>
+        <v>-0.08928686014272214</v>
       </c>
       <c r="H26" t="n">
         <v>24</v>
@@ -1115,7 +1115,7 @@
         <v>45701</v>
       </c>
       <c r="B27" t="n">
-        <v>0.1161741662799719</v>
+        <v>0.1161741662793069</v>
       </c>
       <c r="C27" t="n">
         <v>24</v>
@@ -1127,10 +1127,10 @@
         <v>0.1095250000000032</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1276484356297941</v>
+        <v>0.1276484356677041</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.3464894268176051</v>
+        <v>-0.3464894276173873</v>
       </c>
       <c r="H27" t="n">
         <v>24</v>
@@ -1141,7 +1141,7 @@
         <v>45702</v>
       </c>
       <c r="B28" t="n">
-        <v>0.3620777727390532</v>
+        <v>0.362077772636947</v>
       </c>
       <c r="C28" t="n">
         <v>24</v>
@@ -1150,13 +1150,13 @@
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>0.337327666726809</v>
+        <v>0.3373276666339269</v>
       </c>
       <c r="F28" t="n">
-        <v>0.6580835169566702</v>
+        <v>0.6580835168947987</v>
       </c>
       <c r="G28" t="n">
-        <v>0.3361297056469769</v>
+        <v>0.3361297057718079</v>
       </c>
       <c r="H28" t="n">
         <v>24</v>
@@ -1167,7 +1167,7 @@
         <v>45703</v>
       </c>
       <c r="B29" t="n">
-        <v>0.07084480950939435</v>
+        <v>0.07084480960819853</v>
       </c>
       <c r="C29" t="n">
         <v>24</v>
@@ -1176,13 +1176,13 @@
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>0.06612616660652471</v>
+        <v>0.06612616669940685</v>
       </c>
       <c r="F29" t="n">
-        <v>0.08849510921150987</v>
+        <v>0.08849510913858338</v>
       </c>
       <c r="G29" t="n">
-        <v>0.09507728524481918</v>
+        <v>0.09507728673626514</v>
       </c>
       <c r="H29" t="n">
         <v>24</v>
@@ -1193,7 +1193,7 @@
         <v>45704</v>
       </c>
       <c r="B30" t="n">
-        <v>0.1311630474181683</v>
+        <v>0.1311630478148062</v>
       </c>
       <c r="C30" t="n">
         <v>24</v>
@@ -1202,13 +1202,13 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>0.1226278330927707</v>
+        <v>0.1226278334642992</v>
       </c>
       <c r="F30" t="n">
-        <v>0.1439071916650078</v>
+        <v>0.1439071917352525</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.07555510977072233</v>
+        <v>-0.07555511082073463</v>
       </c>
       <c r="H30" t="n">
         <v>24</v>
@@ -1219,7 +1219,7 @@
         <v>45705</v>
       </c>
       <c r="B31" t="n">
-        <v>0.004555178221486922</v>
+        <v>0.004555179411069307</v>
       </c>
       <c r="C31" t="n">
         <v>24</v>
@@ -1228,13 +1228,13 @@
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>0.004267999278316263</v>
+        <v>0.00426800039290202</v>
       </c>
       <c r="F31" t="n">
-        <v>0.004267999278316262</v>
+        <v>0.00426800039290202</v>
       </c>
       <c r="G31" t="n">
-        <v>0.9893265591646878</v>
+        <v>0.9893265535899602</v>
       </c>
       <c r="H31" t="n">
         <v>24</v>
@@ -1245,7 +1245,7 @@
         <v>45706</v>
       </c>
       <c r="B32" t="n">
-        <v>0.1466494735495411</v>
+        <v>0.1466494733504327</v>
       </c>
       <c r="C32" t="n">
         <v>24</v>
@@ -1254,13 +1254,13 @@
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>0.1373916667869472</v>
+        <v>0.1373916666011829</v>
       </c>
       <c r="F32" t="n">
-        <v>0.16904562011422</v>
+        <v>0.1690456200542201</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.6260072355031556</v>
+        <v>-0.6260072343489065</v>
       </c>
       <c r="H32" t="n">
         <v>24</v>
@@ -1271,7 +1271,7 @@
         <v>45707</v>
       </c>
       <c r="B33" t="n">
-        <v>0.2817211314803789</v>
+        <v>0.2817211314805435</v>
       </c>
       <c r="C33" t="n">
         <v>24</v>
@@ -1283,10 +1283,10 @@
         <v>0.2700708333333329</v>
       </c>
       <c r="F33" t="n">
-        <v>0.543949598097258</v>
+        <v>0.543949598305229</v>
       </c>
       <c r="G33" t="n">
-        <v>0.7657141129753632</v>
+        <v>0.7657141127962117</v>
       </c>
       <c r="H33" t="n">
         <v>24</v>
@@ -1297,7 +1297,7 @@
         <v>45708</v>
       </c>
       <c r="B34" t="n">
-        <v>0.1285190553453263</v>
+        <v>0.1285190553443407</v>
       </c>
       <c r="C34" t="n">
         <v>24</v>
@@ -1309,10 +1309,10 @@
         <v>0.1232124999999975</v>
       </c>
       <c r="F34" t="n">
-        <v>0.1484189776836599</v>
+        <v>0.1484189775796189</v>
       </c>
       <c r="G34" t="n">
-        <v>0.5747536766956036</v>
+        <v>0.5747536772917949</v>
       </c>
       <c r="H34" t="n">
         <v>24</v>
@@ -1323,7 +1323,7 @@
         <v>45709</v>
       </c>
       <c r="B35" t="n">
-        <v>0.1578571474486418</v>
+        <v>0.1578571473506362</v>
       </c>
       <c r="C35" t="n">
         <v>24</v>
@@ -1332,13 +1332,13 @@
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>0.150829166726807</v>
+        <v>0.1508291666339249</v>
       </c>
       <c r="F35" t="n">
-        <v>0.1849014411244309</v>
+        <v>0.1849014410691993</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.5756869774943114</v>
+        <v>-0.5756869765529706</v>
       </c>
       <c r="H35" t="n">
         <v>24</v>
@@ -1349,7 +1349,7 @@
         <v>45710</v>
       </c>
       <c r="B36" t="n">
-        <v>0.2251531844037445</v>
+        <v>0.2251531843058326</v>
       </c>
       <c r="C36" t="n">
         <v>24</v>
@@ -1358,13 +1358,13 @@
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>0.2159958333934746</v>
+        <v>0.2159958333005925</v>
       </c>
       <c r="F36" t="n">
-        <v>0.30765087147679</v>
+        <v>0.3076508715510139</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.1525389108845354</v>
+        <v>-0.1525389114406597</v>
       </c>
       <c r="H36" t="n">
         <v>24</v>
@@ -1375,7 +1375,7 @@
         <v>45711</v>
       </c>
       <c r="B37" t="n">
-        <v>2.65653934040734</v>
+        <v>2.656539340288854</v>
       </c>
       <c r="C37" t="n">
         <v>24</v>
@@ -1384,13 +1384,13 @@
         <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>2.216300000060141</v>
+        <v>2.216299999967259</v>
       </c>
       <c r="F37" t="n">
-        <v>5.225608237350632</v>
+        <v>5.225608237341996</v>
       </c>
       <c r="G37" t="n">
-        <v>0.5557845060167694</v>
+        <v>0.5557845060182377</v>
       </c>
       <c r="H37" t="n">
         <v>24</v>
@@ -1401,7 +1401,7 @@
         <v>45712</v>
       </c>
       <c r="B38" t="n">
-        <v>0.336591195439681</v>
+        <v>0.3365911956314889</v>
       </c>
       <c r="C38" t="n">
         <v>24</v>
@@ -1410,13 +1410,13 @@
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>0.3202749998797199</v>
+        <v>0.3202750000654842</v>
       </c>
       <c r="F38" t="n">
-        <v>0.5233157722189757</v>
+        <v>0.523315772288125</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.07642443126762477</v>
+        <v>-0.076424431552095</v>
       </c>
       <c r="H38" t="n">
         <v>24</v>
@@ -1427,7 +1427,7 @@
         <v>45713</v>
       </c>
       <c r="B39" t="n">
-        <v>0.2833397966920618</v>
+        <v>0.2833397963021936</v>
       </c>
       <c r="C39" t="n">
         <v>24</v>
@@ -1436,13 +1436,13 @@
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>0.2709166669072284</v>
+        <v>0.2709166665356998</v>
       </c>
       <c r="F39" t="n">
-        <v>0.4078487761077886</v>
+        <v>0.4078487760965155</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.9377110400384834</v>
+        <v>-0.937711039931366</v>
       </c>
       <c r="H39" t="n">
         <v>24</v>
@@ -1453,7 +1453,7 @@
         <v>45714</v>
       </c>
       <c r="B40" t="n">
-        <v>0.1810833610458345</v>
+        <v>0.1810833611410702</v>
       </c>
       <c r="C40" t="n">
         <v>24</v>
@@ -1462,13 +1462,13 @@
         <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>0.1739791666065281</v>
+        <v>0.1739791666994102</v>
       </c>
       <c r="F40" t="n">
-        <v>0.2313673909444823</v>
+        <v>0.2313673909140324</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.7164541498526882</v>
+        <v>-0.7164541494008885</v>
       </c>
       <c r="H40" t="n">
         <v>24</v>
@@ -1479,7 +1479,7 @@
         <v>45715</v>
       </c>
       <c r="B41" t="n">
-        <v>0.2037930624334398</v>
+        <v>0.2037930621413329</v>
       </c>
       <c r="C41" t="n">
         <v>24</v>
@@ -1488,13 +1488,13 @@
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>0.1950875001804189</v>
+        <v>0.1950874999017724</v>
       </c>
       <c r="F41" t="n">
-        <v>0.2499121387945386</v>
+        <v>0.2499121386909386</v>
       </c>
       <c r="G41" t="n">
-        <v>0.2062257981843277</v>
+        <v>0.2062257988424392</v>
       </c>
       <c r="H41" t="n">
         <v>24</v>
@@ -1505,7 +1505,7 @@
         <v>45716</v>
       </c>
       <c r="B42" t="n">
-        <v>2.647760380224817</v>
+        <v>2.647760380591345</v>
       </c>
       <c r="C42" t="n">
         <v>24</v>
@@ -1514,13 +1514,13 @@
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>3.153083333092773</v>
+        <v>3.153083333464302</v>
       </c>
       <c r="F42" t="n">
-        <v>6.450563883984152</v>
+        <v>6.450563884120537</v>
       </c>
       <c r="G42" t="n">
-        <v>0.8071940086114268</v>
+        <v>0.8071940086032738</v>
       </c>
       <c r="H42" t="n">
         <v>24</v>
@@ -1531,7 +1531,7 @@
         <v>45717</v>
       </c>
       <c r="B43" t="n">
-        <v>0.8065072859619082</v>
+        <v>0.8065072860328781</v>
       </c>
       <c r="C43" t="n">
         <v>24</v>
@@ -1540,13 +1540,13 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>1.021645833273199</v>
+        <v>1.021645833366081</v>
       </c>
       <c r="F43" t="n">
-        <v>1.960039235619275</v>
+        <v>1.960039236045963</v>
       </c>
       <c r="G43" t="n">
-        <v>0.9377079500025586</v>
+        <v>0.9377079499754374</v>
       </c>
       <c r="H43" t="n">
         <v>24</v>
@@ -1557,7 +1557,7 @@
         <v>45718</v>
       </c>
       <c r="B44" t="n">
-        <v>0.178787636144849</v>
+        <v>0.1787876362137393</v>
       </c>
       <c r="C44" t="n">
         <v>24</v>
@@ -1566,13 +1566,13 @@
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>0.2396249999398575</v>
+        <v>0.2396250000327396</v>
       </c>
       <c r="F44" t="n">
-        <v>0.4415098620047797</v>
+        <v>0.4415098621549445</v>
       </c>
       <c r="G44" t="n">
-        <v>-5.479345954573618</v>
+        <v>-5.479345958981086</v>
       </c>
       <c r="H44" t="n">
         <v>24</v>
@@ -1583,7 +1583,7 @@
         <v>45719</v>
       </c>
       <c r="B45" t="n">
-        <v>0.3160022392732735</v>
+        <v>0.3160022392014578</v>
       </c>
       <c r="C45" t="n">
         <v>24</v>
@@ -1592,13 +1592,13 @@
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>0.408591666726803</v>
+        <v>0.4085916666339209</v>
       </c>
       <c r="F45" t="n">
-        <v>1.14698657011859</v>
+        <v>1.146986569872348</v>
       </c>
       <c r="G45" t="n">
-        <v>0.8137277173711128</v>
+        <v>0.813727717451093</v>
       </c>
       <c r="H45" t="n">
         <v>24</v>
@@ -1609,7 +1609,7 @@
         <v>45720</v>
       </c>
       <c r="B46" t="n">
-        <v>0.4004935203408689</v>
+        <v>0.4004935204867768</v>
       </c>
       <c r="C46" t="n">
         <v>24</v>
@@ -1618,13 +1618,13 @@
         <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>0.4911208332130528</v>
+        <v>0.4911208333988171</v>
       </c>
       <c r="F46" t="n">
-        <v>1.159795853104691</v>
+        <v>1.159795852796969</v>
       </c>
       <c r="G46" t="n">
-        <v>0.886203095670656</v>
+        <v>0.8862030957310423</v>
       </c>
       <c r="H46" t="n">
         <v>24</v>
@@ -1635,7 +1635,7 @@
         <v>45721</v>
       </c>
       <c r="B47" t="n">
-        <v>0.178294736661153</v>
+        <v>0.1782947365053299</v>
       </c>
       <c r="C47" t="n">
         <v>24</v>
@@ -1644,13 +1644,13 @@
         <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>0.2136291667869443</v>
+        <v>0.21362916660118</v>
       </c>
       <c r="F47" t="n">
-        <v>0.2566121190387541</v>
+        <v>0.2566121188755666</v>
       </c>
       <c r="G47" t="n">
-        <v>0.24866418562373</v>
+        <v>0.2486641865793254</v>
       </c>
       <c r="H47" t="n">
         <v>24</v>
@@ -1661,7 +1661,7 @@
         <v>45722</v>
       </c>
       <c r="B48" t="n">
-        <v>0.1812195288707588</v>
+        <v>0.1812195287919004</v>
       </c>
       <c r="C48" t="n">
         <v>24</v>
@@ -1670,13 +1670,13 @@
         <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>0.2167250000601383</v>
+        <v>0.2167249999672561</v>
       </c>
       <c r="F48" t="n">
-        <v>0.2545779660320834</v>
+        <v>0.2545779661664567</v>
       </c>
       <c r="G48" t="n">
-        <v>0.02099345902889438</v>
+        <v>0.02099345799540042</v>
       </c>
       <c r="H48" t="n">
         <v>24</v>
@@ -1687,7 +1687,7 @@
         <v>45723</v>
       </c>
       <c r="B49" t="n">
-        <v>0.1426548903899104</v>
+        <v>0.1426548902347121</v>
       </c>
       <c r="C49" t="n">
         <v>24</v>
@@ -1696,13 +1696,13 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>0.1716666667869511</v>
+        <v>0.1716666666011868</v>
       </c>
       <c r="F49" t="n">
-        <v>0.207012127229901</v>
+        <v>0.2070121272787173</v>
       </c>
       <c r="G49" t="n">
-        <v>0.02731182135697685</v>
+        <v>0.02731182089823003</v>
       </c>
       <c r="H49" t="n">
         <v>24</v>
@@ -1713,7 +1713,7 @@
         <v>45724</v>
       </c>
       <c r="B50" t="n">
-        <v>0.219279509769354</v>
+        <v>0.2192795098458388</v>
       </c>
       <c r="C50" t="n">
         <v>24</v>
@@ -1722,13 +1722,13 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>0.263024999939861</v>
+        <v>0.2630250000327432</v>
       </c>
       <c r="F50" t="n">
-        <v>0.3460975621408592</v>
+        <v>0.3460975620965782</v>
       </c>
       <c r="G50" t="n">
-        <v>-0.4128439069168095</v>
+        <v>-0.41284390655528</v>
       </c>
       <c r="H50" t="n">
         <v>24</v>
@@ -1739,7 +1739,7 @@
         <v>45725</v>
       </c>
       <c r="B51" t="n">
-        <v>0.1470394123450915</v>
+        <v>0.147039412422251</v>
       </c>
       <c r="C51" t="n">
         <v>24</v>
@@ -1748,13 +1748,13 @@
         <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>0.176079166606525</v>
+        <v>0.1760791666994071</v>
       </c>
       <c r="F51" t="n">
-        <v>0.2281760769659339</v>
+        <v>0.2281760769110006</v>
       </c>
       <c r="G51" t="n">
-        <v>-0.2747694374141108</v>
+        <v>-0.2747694368003111</v>
       </c>
       <c r="H51" t="n">
         <v>24</v>
@@ -1765,7 +1765,7 @@
         <v>45726</v>
       </c>
       <c r="B52" t="n">
-        <v>0.1487615581434885</v>
+        <v>0.1487615580651762</v>
       </c>
       <c r="C52" t="n">
         <v>24</v>
@@ -1774,13 +1774,13 @@
         <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>0.1782125000601376</v>
+        <v>0.1782124999672554</v>
       </c>
       <c r="F52" t="n">
-        <v>0.2247371195706378</v>
+        <v>0.2247371195835532</v>
       </c>
       <c r="G52" t="n">
-        <v>-1.177165623630884</v>
+        <v>-1.177165623881123</v>
       </c>
       <c r="H52" t="n">
         <v>24</v>
@@ -1791,7 +1791,7 @@
         <v>45727</v>
       </c>
       <c r="B53" t="n">
-        <v>0.2107082224579345</v>
+        <v>0.2107082223796743</v>
       </c>
       <c r="C53" t="n">
         <v>24</v>
@@ -1800,13 +1800,13 @@
         <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>0.2523166667268093</v>
+        <v>0.2523166666339272</v>
       </c>
       <c r="F53" t="n">
-        <v>0.3189321557927244</v>
+        <v>0.3189321557961318</v>
       </c>
       <c r="G53" t="n">
-        <v>-0.8251978596021381</v>
+        <v>-0.8251978596411382</v>
       </c>
       <c r="H53" t="n">
         <v>24</v>
@@ -1817,7 +1817,7 @@
         <v>45728</v>
       </c>
       <c r="B54" t="n">
-        <v>4.821719824739232</v>
+        <v>4.821719824623724</v>
       </c>
       <c r="C54" t="n">
         <v>24</v>
@@ -1826,13 +1826,13 @@
         <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>5.128925000060138</v>
+        <v>5.128924999967256</v>
       </c>
       <c r="F54" t="n">
-        <v>9.927852600627928</v>
+        <v>9.927852600627693</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.1212197710811225</v>
+        <v>-0.1212197710810696</v>
       </c>
       <c r="H54" t="n">
         <v>24</v>
@@ -1843,7 +1843,7 @@
         <v>45729</v>
       </c>
       <c r="B55" t="n">
-        <v>0.7343777834640847</v>
+        <v>0.7343777860589428</v>
       </c>
       <c r="C55" t="n">
         <v>24</v>
@@ -1852,13 +1852,13 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>0.7990000000024242</v>
+        <v>0.7990000031905063</v>
       </c>
       <c r="F55" t="n">
-        <v>2.871676839095814</v>
+        <v>2.87167683674366</v>
       </c>
       <c r="G55" t="n">
-        <v>0.7479627219580163</v>
+        <v>0.7479627223708973</v>
       </c>
       <c r="H55" t="n">
         <v>24</v>
@@ -1869,7 +1869,7 @@
         <v>45730</v>
       </c>
       <c r="B56" t="n">
-        <v>0.5360892684071833</v>
+        <v>0.5360892793351079</v>
       </c>
       <c r="C56" t="n">
         <v>24</v>
@@ -1878,13 +1878,13 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>0.6100416665526733</v>
+        <v>0.6100416787580922</v>
       </c>
       <c r="F56" t="n">
-        <v>1.451740962774442</v>
+        <v>1.451740985926893</v>
       </c>
       <c r="G56" t="n">
-        <v>0.9317300592937534</v>
+        <v>0.9317300571162073</v>
       </c>
       <c r="H56" t="n">
         <v>24</v>
@@ -1895,7 +1895,7 @@
         <v>45731</v>
       </c>
       <c r="B57" t="n">
-        <v>0.1557916662689601</v>
+        <v>0.1557916688767045</v>
       </c>
       <c r="C57" t="n">
         <v>24</v>
@@ -1904,13 +1904,13 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>0.1835708334226111</v>
+        <v>0.183570836478968</v>
       </c>
       <c r="F57" t="n">
-        <v>0.219559592403693</v>
+        <v>0.2195595948834969</v>
       </c>
       <c r="G57" t="n">
-        <v>-0.9723873938404632</v>
+        <v>-0.972387438394507</v>
       </c>
       <c r="H57" t="n">
         <v>24</v>
@@ -1921,7 +1921,7 @@
         <v>45732</v>
       </c>
       <c r="B58" t="n">
-        <v>1.31443107522064</v>
+        <v>1.314431075320934</v>
       </c>
       <c r="C58" t="n">
         <v>24</v>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="E58" t="n">
-        <v>1.50227916675106</v>
+        <v>1.502279166909198</v>
       </c>
       <c r="F58" t="n">
-        <v>3.241942713101215</v>
+        <v>3.241942712851427</v>
       </c>
       <c r="G58" t="n">
-        <v>-0.2117985693582725</v>
+        <v>-0.2117985691715374</v>
       </c>
       <c r="H58" t="n">
         <v>24</v>
@@ -1947,7 +1947,7 @@
         <v>45733</v>
       </c>
       <c r="B59" t="n">
-        <v>1.169798519625096</v>
+        <v>1.169798519918225</v>
       </c>
       <c r="C59" t="n">
         <v>24</v>
@@ -1956,13 +1956,13 @@
         <v>0</v>
       </c>
       <c r="E59" t="n">
-        <v>1.128075000208577</v>
+        <v>1.128075000626945</v>
       </c>
       <c r="F59" t="n">
-        <v>4.654734818927892</v>
+        <v>4.654734818416024</v>
       </c>
       <c r="G59" t="n">
-        <v>0.8016554523423554</v>
+        <v>0.8016554523859782</v>
       </c>
       <c r="H59" t="n">
         <v>24</v>
@@ -1973,7 +1973,7 @@
         <v>45734</v>
       </c>
       <c r="B60" t="n">
-        <v>1.054321845871975</v>
+        <v>1.054321845898978</v>
       </c>
       <c r="C60" t="n">
         <v>24</v>
@@ -1982,13 +1982,13 @@
         <v>0</v>
       </c>
       <c r="E60" t="n">
-        <v>1.229545833333335</v>
+        <v>1.229545833366076</v>
       </c>
       <c r="F60" t="n">
-        <v>4.639849804022194</v>
+        <v>4.639849804277144</v>
       </c>
       <c r="G60" t="n">
-        <v>0.8452292209226818</v>
+        <v>0.8452292209056732</v>
       </c>
       <c r="H60" t="n">
         <v>24</v>
@@ -1999,7 +1999,7 @@
         <v>45735</v>
       </c>
       <c r="B61" t="n">
-        <v>0.6315206889837534</v>
+        <v>0.6315206933026812</v>
       </c>
       <c r="C61" t="n">
         <v>24</v>
@@ -2008,13 +2008,13 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>0.7073916667243031</v>
+        <v>0.7073916717780241</v>
       </c>
       <c r="F61" t="n">
-        <v>1.918466581520136</v>
+        <v>1.918466587027653</v>
       </c>
       <c r="G61" t="n">
-        <v>0.6067268537686004</v>
+        <v>0.6067268515105901</v>
       </c>
       <c r="H61" t="n">
         <v>24</v>
@@ -2025,7 +2025,7 @@
         <v>45736</v>
       </c>
       <c r="B62" t="n">
-        <v>0.1849193381527482</v>
+        <v>0.1849189580581324</v>
       </c>
       <c r="C62" t="n">
         <v>24</v>
@@ -2034,13 +2034,13 @@
         <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>0.1976375047104248</v>
+        <v>0.1976370978541849</v>
       </c>
       <c r="F62" t="n">
-        <v>0.2229592489776799</v>
+        <v>0.2229591310810682</v>
       </c>
       <c r="G62" t="n">
-        <v>-0.5860854015891741</v>
+        <v>-0.5860837242060095</v>
       </c>
       <c r="H62" t="n">
         <v>24</v>
@@ -2051,7 +2051,7 @@
         <v>45737</v>
       </c>
       <c r="B63" t="n">
-        <v>0.8000884548339671</v>
+        <v>0.8000879229137839</v>
       </c>
       <c r="C63" t="n">
         <v>24</v>
@@ -2060,13 +2060,13 @@
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>0.7652999997259009</v>
+        <v>0.7652994355263575</v>
       </c>
       <c r="F63" t="n">
-        <v>2.411142689798054</v>
+        <v>2.411142444736559</v>
       </c>
       <c r="G63" t="n">
-        <v>0.8044400996165804</v>
+        <v>0.8044401393688516</v>
       </c>
       <c r="H63" t="n">
         <v>24</v>
@@ -2077,7 +2077,7 @@
         <v>45738</v>
       </c>
       <c r="B64" t="n">
-        <v>0.6189796968320547</v>
+        <v>0.6189796974620088</v>
       </c>
       <c r="C64" t="n">
         <v>24</v>
@@ -2086,13 +2086,13 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>0.6425624998578906</v>
+        <v>0.6425625004899137</v>
       </c>
       <c r="F64" t="n">
-        <v>1.76391844015623</v>
+        <v>1.763918442008615</v>
       </c>
       <c r="G64" t="n">
-        <v>0.8430956796798323</v>
+        <v>0.8430956793502852</v>
       </c>
       <c r="H64" t="n">
         <v>24</v>
@@ -2103,7 +2103,7 @@
         <v>45739</v>
       </c>
       <c r="B65" t="n">
-        <v>2.084153717469959</v>
+        <v>2.084153717772416</v>
       </c>
       <c r="C65" t="n">
         <v>24</v>
@@ -2112,13 +2112,13 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>2.464458333263001</v>
+        <v>2.464458333623161</v>
       </c>
       <c r="F65" t="n">
-        <v>3.997438486913246</v>
+        <v>3.997438487341991</v>
       </c>
       <c r="G65" t="n">
-        <v>0.8825467727999216</v>
+        <v>0.8825467727747267</v>
       </c>
       <c r="H65" t="n">
         <v>24</v>
@@ -2129,7 +2129,7 @@
         <v>45740</v>
       </c>
       <c r="B66" t="n">
-        <v>0.8334790373059167</v>
+        <v>0.833479037299942</v>
       </c>
       <c r="C66" t="n">
         <v>24</v>
@@ -2141,10 +2141,10 @@
         <v>1.018691666666664</v>
       </c>
       <c r="F66" t="n">
-        <v>2.394364470399276</v>
+        <v>2.394364469986946</v>
       </c>
       <c r="G66" t="n">
-        <v>0.9349125756205449</v>
+        <v>0.9349125756429622</v>
       </c>
       <c r="H66" t="n">
         <v>24</v>
@@ -2155,7 +2155,7 @@
         <v>45741</v>
       </c>
       <c r="B67" t="n">
-        <v>0.8204401421705483</v>
+        <v>0.8204401420142344</v>
       </c>
       <c r="C67" t="n">
         <v>24</v>
@@ -2164,13 +2164,13 @@
         <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>0.9044458334531184</v>
+        <v>0.9044458332787606</v>
       </c>
       <c r="F67" t="n">
-        <v>2.761535610023544</v>
+        <v>2.761535610020261</v>
       </c>
       <c r="G67" t="n">
-        <v>-1.081610607512095</v>
+        <v>-1.081610607507146</v>
       </c>
       <c r="H67" t="n">
         <v>24</v>
@@ -2181,7 +2181,7 @@
         <v>45742</v>
       </c>
       <c r="B68" t="n">
-        <v>0.1306757271066566</v>
+        <v>0.1306757272673802</v>
       </c>
       <c r="C68" t="n">
         <v>24</v>
@@ -2190,13 +2190,13 @@
         <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>0.1503083332130532</v>
+        <v>0.1503083333988175</v>
       </c>
       <c r="F68" t="n">
-        <v>0.1953455526947083</v>
+        <v>0.1953455528623136</v>
       </c>
       <c r="G68" t="n">
-        <v>-0.0987334979263268</v>
+        <v>-0.09873349981174062</v>
       </c>
       <c r="H68" t="n">
         <v>24</v>
@@ -2207,7 +2207,7 @@
         <v>45743</v>
       </c>
       <c r="B69" t="n">
-        <v>0.8525958854456912</v>
+        <v>0.8525958890901535</v>
       </c>
       <c r="C69" t="n">
         <v>24</v>
@@ -2216,13 +2216,13 @@
         <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>0.9414374999703993</v>
+        <v>0.9414375041606308</v>
       </c>
       <c r="F69" t="n">
-        <v>2.760816806147507</v>
+        <v>2.760816806153016</v>
       </c>
       <c r="G69" t="n">
-        <v>-0.9701879733014036</v>
+        <v>-0.9701879733092669</v>
       </c>
       <c r="H69" t="n">
         <v>24</v>
@@ -2233,7 +2233,7 @@
         <v>45744</v>
       </c>
       <c r="B70" t="n">
-        <v>0.8333314732426175</v>
+        <v>0.8333314963133659</v>
       </c>
       <c r="C70" t="n">
         <v>24</v>
@@ -2242,13 +2242,13 @@
         <v>0</v>
       </c>
       <c r="E70" t="n">
-        <v>0.9208208335331918</v>
+        <v>0.9208208601064291</v>
       </c>
       <c r="F70" t="n">
-        <v>2.818953961355986</v>
+        <v>2.818953962340006</v>
       </c>
       <c r="G70" t="n">
-        <v>-1.085601309613507</v>
+        <v>-1.085601311069559</v>
       </c>
       <c r="H70" t="n">
         <v>24</v>
@@ -2259,7 +2259,7 @@
         <v>45745</v>
       </c>
       <c r="B71" t="n">
-        <v>0.358200894993455</v>
+        <v>0.3582008965952561</v>
       </c>
       <c r="C71" t="n">
         <v>24</v>
@@ -2268,13 +2268,13 @@
         <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>0.4263083332518587</v>
+        <v>0.4263083351401971</v>
       </c>
       <c r="F71" t="n">
-        <v>0.7821387571036067</v>
+        <v>0.7821387599215773</v>
       </c>
       <c r="G71" t="n">
-        <v>0.7893201364087069</v>
+        <v>0.7893201348905885</v>
       </c>
       <c r="H71" t="n">
         <v>24</v>
@@ -2285,7 +2285,7 @@
         <v>45746</v>
       </c>
       <c r="B72" t="n">
-        <v>0.1877071314114798</v>
+        <v>0.1877071313155858</v>
       </c>
       <c r="C72" t="n">
         <v>24</v>
@@ -2294,13 +2294,13 @@
         <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>0.2253708333934785</v>
+        <v>0.2253708332787685</v>
       </c>
       <c r="F72" t="n">
-        <v>0.2664446275993527</v>
+        <v>0.2664446274638991</v>
       </c>
       <c r="G72" t="n">
-        <v>-1.054667128145947</v>
+        <v>-1.054667126056867</v>
       </c>
       <c r="H72" t="n">
         <v>24</v>
@@ -2311,7 +2311,7 @@
         <v>45747</v>
       </c>
       <c r="B73" t="n">
-        <v>0.1321681171851038</v>
+        <v>0.1321681177290456</v>
       </c>
       <c r="C73" t="n">
         <v>24</v>
@@ -2320,13 +2320,13 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>0.1586374999412564</v>
+        <v>0.1586375005929851</v>
       </c>
       <c r="F73" t="n">
-        <v>0.1884726007725817</v>
+        <v>0.1884726016079703</v>
       </c>
       <c r="G73" t="n">
-        <v>-0.7072353995220493</v>
+        <v>-0.7072354146563971</v>
       </c>
       <c r="H73" t="n">
         <v>24</v>
@@ -2337,7 +2337,7 @@
         <v>45748</v>
       </c>
       <c r="B74" t="n">
-        <v>0.1480311969511916</v>
+        <v>0.1480311974403477</v>
       </c>
       <c r="C74" t="n">
         <v>24</v>
@@ -2346,13 +2346,13 @@
         <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>0.1775166667801222</v>
+        <v>0.177516667360304</v>
       </c>
       <c r="F74" t="n">
-        <v>0.2167029073301669</v>
+        <v>0.216702906044337</v>
       </c>
       <c r="G74" t="n">
-        <v>0.3695303093844405</v>
+        <v>0.3695303168663591</v>
       </c>
       <c r="H74" t="n">
         <v>24</v>
@@ -2363,7 +2363,7 @@
         <v>45749</v>
       </c>
       <c r="B75" t="n">
-        <v>0.1704712908590625</v>
+        <v>0.1704712910132941</v>
       </c>
       <c r="C75" t="n">
         <v>24</v>
@@ -2372,13 +2372,13 @@
         <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>0.204645833213051</v>
+        <v>0.2046458333988153</v>
       </c>
       <c r="F75" t="n">
-        <v>0.2544472202356316</v>
+        <v>0.2544472203297924</v>
       </c>
       <c r="G75" t="n">
-        <v>0.1378958509712617</v>
+        <v>0.1378958503332008</v>
       </c>
       <c r="H75" t="n">
         <v>24</v>
@@ -2389,7 +2389,7 @@
         <v>45750</v>
       </c>
       <c r="B76" t="n">
-        <v>0.1036358710628074</v>
+        <v>0.1036358712168765</v>
       </c>
       <c r="C76" t="n">
         <v>24</v>
@@ -2398,13 +2398,13 @@
         <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>0.1247874998797164</v>
+        <v>0.1247875000654807</v>
       </c>
       <c r="F76" t="n">
-        <v>0.1496623935475549</v>
+        <v>0.1496623937588419</v>
       </c>
       <c r="G76" t="n">
-        <v>0.6316250881335241</v>
+        <v>0.6316250870934119</v>
       </c>
       <c r="H76" t="n">
         <v>24</v>
@@ -2415,7 +2415,7 @@
         <v>45751</v>
       </c>
       <c r="B77" t="n">
-        <v>0.08793839478903805</v>
+        <v>0.08793839478912877</v>
       </c>
       <c r="C77" t="n">
         <v>24</v>
@@ -2427,10 +2427,10 @@
         <v>0.1058583333333321</v>
       </c>
       <c r="F77" t="n">
-        <v>0.1471643583382592</v>
+        <v>0.1471643581715105</v>
       </c>
       <c r="G77" t="n">
-        <v>0.481979032714846</v>
+        <v>0.4819790338887622</v>
       </c>
       <c r="H77" t="n">
         <v>24</v>
@@ -2441,7 +2441,7 @@
         <v>45752</v>
       </c>
       <c r="B78" t="n">
-        <v>0.1507849259828458</v>
+        <v>0.1507849259822211</v>
       </c>
       <c r="C78" t="n">
         <v>24</v>
@@ -2453,10 +2453,10 @@
         <v>0.1807124999999991</v>
       </c>
       <c r="F78" t="n">
-        <v>0.2172255692913405</v>
+        <v>0.2172255691588109</v>
       </c>
       <c r="G78" t="n">
-        <v>-0.03206649514514281</v>
+        <v>-0.0320664938858124</v>
       </c>
       <c r="H78" t="n">
         <v>24</v>
@@ -2467,7 +2467,7 @@
         <v>45753</v>
       </c>
       <c r="B79" t="n">
-        <v>0.3487032841423967</v>
+        <v>0.3487032842177513</v>
       </c>
       <c r="C79" t="n">
         <v>24</v>
@@ -2476,13 +2476,13 @@
         <v>0</v>
       </c>
       <c r="E79" t="n">
-        <v>0.4152458332731926</v>
+        <v>0.4152458333660747</v>
       </c>
       <c r="F79" t="n">
-        <v>0.9422893533319427</v>
+        <v>0.9422893533433623</v>
       </c>
       <c r="G79" t="n">
-        <v>-0.8365470981996868</v>
+        <v>-0.8365470982442007</v>
       </c>
       <c r="H79" t="n">
         <v>24</v>
@@ -2493,7 +2493,7 @@
         <v>45754</v>
       </c>
       <c r="B80" t="n">
-        <v>0.1098373101888102</v>
+        <v>0.1098373100332325</v>
       </c>
       <c r="C80" t="n">
         <v>24</v>
@@ -2502,13 +2502,13 @@
         <v>0</v>
       </c>
       <c r="E80" t="n">
-        <v>0.1315208334536114</v>
+        <v>0.1315208332678471</v>
       </c>
       <c r="F80" t="n">
-        <v>0.1577785117196539</v>
+        <v>0.1577785116684087</v>
       </c>
       <c r="G80" t="n">
-        <v>-0.04664013883445484</v>
+        <v>-0.04664013815457402</v>
       </c>
       <c r="H80" t="n">
         <v>24</v>
@@ -2519,7 +2519,7 @@
         <v>45755</v>
       </c>
       <c r="B81" t="n">
-        <v>0.1251470534084059</v>
+        <v>0.1251470533304</v>
       </c>
       <c r="C81" t="n">
         <v>24</v>
@@ -2528,13 +2528,13 @@
         <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>0.1497666667268097</v>
+        <v>0.1497666666339275</v>
       </c>
       <c r="F81" t="n">
-        <v>0.1891673421983413</v>
+        <v>0.1891673421124154</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.7565202274975193</v>
+        <v>-0.7565202259017829</v>
       </c>
       <c r="H81" t="n">
         <v>24</v>
@@ -2545,7 +2545,7 @@
         <v>45756</v>
       </c>
       <c r="B82" t="n">
-        <v>0.1097264075079529</v>
+        <v>0.1097264075074623</v>
       </c>
       <c r="C82" t="n">
         <v>24</v>
@@ -2557,10 +2557,10 @@
         <v>0.1314791666666709</v>
       </c>
       <c r="F82" t="n">
-        <v>0.1753076045890332</v>
+        <v>0.1753076046914746</v>
       </c>
       <c r="G82" t="n">
-        <v>-0.4736456915939531</v>
+        <v>-0.4736456933162103</v>
       </c>
       <c r="H82" t="n">
         <v>24</v>
@@ -2571,7 +2571,7 @@
         <v>45757</v>
       </c>
       <c r="B83" t="n">
-        <v>0.1612891231331977</v>
+        <v>0.1612891230919415</v>
       </c>
       <c r="C83" t="n">
         <v>23</v>
@@ -2580,13 +2580,13 @@
         <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>0.1930652174226825</v>
+        <v>0.1930652173742223</v>
       </c>
       <c r="F83" t="n">
-        <v>0.2197731192312188</v>
+        <v>0.2197731191483765</v>
       </c>
       <c r="G83" t="n">
-        <v>-0.9288443197266538</v>
+        <v>-0.9288443182725181</v>
       </c>
       <c r="H83" t="n">
         <v>23</v>
